--- a/output7/【河洛文讀注音-雅俗通】《岳陽樓記》.xlsx
+++ b/output7/【河洛文讀注音-雅俗通】《岳陽樓記》.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5278C90-9A6E-4B7E-8771-D3F63F85C399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272C89F4-6D53-41A2-AD77-131F3C8E2469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="735">
   <si>
     <t>Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -2310,6 +2310,22 @@
   </si>
   <si>
     <t>居一英</t>
+  </si>
+  <si>
+    <t>lik8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>king1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kiu7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2874,15 +2890,6 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2894,6 +2901,15 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4107,14 +4123,18 @@
       <c r="B3" s="20"/>
       <c r="C3" s="21"/>
       <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
+      <c r="E3" s="22" t="s">
+        <v>731</v>
+      </c>
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
       <c r="H3" s="22"/>
       <c r="I3" s="22"/>
       <c r="J3" s="22"/>
       <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
+      <c r="L3" s="22" t="s">
+        <v>732</v>
+      </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
       <c r="O3" s="22"/>
@@ -4122,7 +4142,7 @@
       <c r="Q3" s="22"/>
       <c r="R3" s="22"/>
       <c r="T3" s="24"/>
-      <c r="V3" s="54" t="s">
+      <c r="V3" s="58" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4170,59 +4190,59 @@
       </c>
       <c r="R4" s="26"/>
       <c r="S4" s="27"/>
-      <c r="V4" s="55"/>
+      <c r="V4" s="59"/>
     </row>
     <row r="5" spans="1:22" s="14" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="28">
         <v>1</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="57" t="s">
+      <c r="E5" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="F5" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="G5" s="57" t="s">
+      <c r="G5" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="H5" s="57" t="s">
+      <c r="H5" s="54" t="s">
         <v>89</v>
       </c>
       <c r="I5" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="K5" s="57" t="s">
+      <c r="K5" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="57" t="s">
+      <c r="L5" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="M5" s="57" t="s">
+      <c r="M5" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="N5" s="57" t="s">
+      <c r="N5" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="O5" s="57" t="s">
+      <c r="O5" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="P5" s="57" t="s">
+      <c r="P5" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="Q5" s="57" t="s">
+      <c r="Q5" s="54" t="s">
         <v>96</v>
       </c>
       <c r="R5" s="51" t="s">
         <v>38</v>
       </c>
       <c r="S5" s="29"/>
-      <c r="V5" s="55"/>
+      <c r="V5" s="59"/>
     </row>
     <row r="6" spans="1:22" s="34" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="30"/>
@@ -4269,7 +4289,7 @@
       </c>
       <c r="R6" s="32"/>
       <c r="S6" s="33"/>
-      <c r="V6" s="55"/>
+      <c r="V6" s="59"/>
     </row>
     <row r="7" spans="1:22" s="38" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="35"/>
@@ -4290,7 +4310,7 @@
       <c r="Q7" s="22"/>
       <c r="R7" s="22"/>
       <c r="S7" s="37"/>
-      <c r="V7" s="55"/>
+      <c r="V7" s="59"/>
     </row>
     <row r="8" spans="1:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="25"/>
@@ -4334,61 +4354,61 @@
         <v>336</v>
       </c>
       <c r="S8" s="27"/>
-      <c r="V8" s="55"/>
+      <c r="V8" s="59"/>
     </row>
     <row r="9" spans="1:22" s="14" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="28">
         <f>B5+1</f>
         <v>2</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="D9" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="57" t="s">
+      <c r="E9" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="57" t="s">
+      <c r="F9" s="54" t="s">
         <v>88</v>
       </c>
       <c r="G9" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="57" t="s">
+      <c r="H9" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="54" t="s">
         <v>99</v>
       </c>
-      <c r="J9" s="57" t="s">
+      <c r="J9" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="K9" s="57" t="s">
+      <c r="K9" s="54" t="s">
         <v>37</v>
       </c>
       <c r="L9" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="57" t="s">
+      <c r="M9" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="N9" s="57" t="s">
+      <c r="N9" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="O9" s="57" t="s">
+      <c r="O9" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="P9" s="57" t="s">
+      <c r="P9" s="54" t="s">
         <v>103</v>
       </c>
       <c r="Q9" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="R9" s="57" t="s">
+      <c r="R9" s="54" t="s">
         <v>104</v>
       </c>
       <c r="S9" s="29"/>
       <c r="T9" s="24"/>
-      <c r="V9" s="55"/>
+      <c r="V9" s="59"/>
     </row>
     <row r="10" spans="1:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="30"/>
@@ -4432,7 +4452,7 @@
         <v>526</v>
       </c>
       <c r="S10" s="39"/>
-      <c r="V10" s="55"/>
+      <c r="V10" s="59"/>
     </row>
     <row r="11" spans="1:22" s="37" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="40"/>
@@ -4445,14 +4465,18 @@
       <c r="I11" s="22"/>
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
+      <c r="L11" s="22" t="s">
+        <v>733</v>
+      </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
       <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
+      <c r="P11" s="22" t="s">
+        <v>734</v>
+      </c>
       <c r="Q11" s="22"/>
       <c r="R11" s="22"/>
-      <c r="V11" s="55"/>
+      <c r="V11" s="59"/>
     </row>
     <row r="12" spans="1:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="25"/>
@@ -4498,60 +4522,60 @@
         <v>348</v>
       </c>
       <c r="S12" s="27"/>
-      <c r="V12" s="55"/>
+      <c r="V12" s="59"/>
     </row>
     <row r="13" spans="1:22" s="14" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="28">
         <f>B9+1</f>
         <v>3</v>
       </c>
-      <c r="D13" s="57" t="s">
+      <c r="D13" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="E13" s="57" t="s">
+      <c r="E13" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="F13" s="57" t="s">
+      <c r="F13" s="54" t="s">
         <v>107</v>
       </c>
-      <c r="G13" s="57" t="s">
+      <c r="G13" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="H13" s="57" t="s">
+      <c r="H13" s="54" t="s">
         <v>109</v>
       </c>
       <c r="I13" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="57" t="s">
+      <c r="J13" s="54" t="s">
         <v>110</v>
       </c>
-      <c r="K13" s="57" t="s">
+      <c r="K13" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="L13" s="57" t="s">
+      <c r="L13" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="M13" s="57" t="s">
+      <c r="M13" s="54" t="s">
         <v>113</v>
       </c>
       <c r="N13" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="O13" s="57" t="s">
+      <c r="O13" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="P13" s="57" t="s">
+      <c r="P13" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="Q13" s="57" t="s">
+      <c r="Q13" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="R13" s="57" t="s">
+      <c r="R13" s="54" t="s">
         <v>117</v>
       </c>
       <c r="S13" s="29"/>
-      <c r="V13" s="55"/>
+      <c r="V13" s="59"/>
     </row>
     <row r="14" spans="1:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="30"/>
@@ -4597,7 +4621,7 @@
         <v>539</v>
       </c>
       <c r="S14" s="39"/>
-      <c r="V14" s="55"/>
+      <c r="V14" s="59"/>
     </row>
     <row r="15" spans="1:22" s="43" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="20"/>
@@ -4617,7 +4641,7 @@
       <c r="P15" s="22"/>
       <c r="Q15" s="22"/>
       <c r="R15" s="22"/>
-      <c r="V15" s="55"/>
+      <c r="V15" s="59"/>
     </row>
     <row r="16" spans="1:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="25"/>
@@ -4663,60 +4687,60 @@
       </c>
       <c r="R16" s="26"/>
       <c r="S16" s="27"/>
-      <c r="V16" s="55"/>
+      <c r="V16" s="59"/>
     </row>
     <row r="17" spans="2:22" s="14" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="28">
         <f>B13+1</f>
         <v>4</v>
       </c>
-      <c r="D17" s="57" t="s">
+      <c r="D17" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="57" t="s">
+      <c r="E17" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="F17" s="57" t="s">
+      <c r="F17" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="G17" s="57" t="s">
+      <c r="G17" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="H17" s="57" t="s">
+      <c r="H17" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="I17" s="57" t="s">
+      <c r="I17" s="54" t="s">
         <v>26</v>
       </c>
       <c r="J17" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="K17" s="57" t="s">
+      <c r="K17" s="54" t="s">
         <v>122</v>
       </c>
-      <c r="L17" s="57" t="s">
+      <c r="L17" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="M17" s="57" t="s">
+      <c r="M17" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="N17" s="57" t="s">
+      <c r="N17" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="O17" s="57" t="s">
+      <c r="O17" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="P17" s="57" t="s">
+      <c r="P17" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="Q17" s="57" t="s">
+      <c r="Q17" s="54" t="s">
         <v>126</v>
       </c>
       <c r="R17" s="51" t="s">
         <v>38</v>
       </c>
       <c r="S17" s="29"/>
-      <c r="V17" s="55"/>
+      <c r="V17" s="59"/>
     </row>
     <row r="18" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="30"/>
@@ -4762,7 +4786,7 @@
       </c>
       <c r="R18" s="32"/>
       <c r="S18" s="39"/>
-      <c r="V18" s="55"/>
+      <c r="V18" s="59"/>
     </row>
     <row r="19" spans="2:22" s="43" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="20"/>
@@ -4782,7 +4806,7 @@
       <c r="P19" s="22"/>
       <c r="Q19" s="22"/>
       <c r="R19" s="22"/>
-      <c r="V19" s="55"/>
+      <c r="V19" s="59"/>
     </row>
     <row r="20" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="25"/>
@@ -4802,7 +4826,7 @@
       <c r="Q20" s="26"/>
       <c r="R20" s="26"/>
       <c r="S20" s="27"/>
-      <c r="V20" s="55"/>
+      <c r="V20" s="59"/>
     </row>
     <row r="21" spans="2:22" s="14" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="28">
@@ -4827,7 +4851,7 @@
       <c r="Q21" s="51"/>
       <c r="R21" s="51"/>
       <c r="S21" s="29"/>
-      <c r="V21" s="55"/>
+      <c r="V21" s="59"/>
     </row>
     <row r="22" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="30"/>
@@ -4847,7 +4871,7 @@
       <c r="Q22" s="32"/>
       <c r="R22" s="32"/>
       <c r="S22" s="39"/>
-      <c r="V22" s="56"/>
+      <c r="V22" s="60"/>
     </row>
     <row r="23" spans="2:22" s="43" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="20"/>
@@ -5017,49 +5041,49 @@
         <f>B25+1</f>
         <v>7</v>
       </c>
-      <c r="D29" s="57" t="s">
+      <c r="D29" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="57" t="s">
+      <c r="E29" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="F29" s="57" t="s">
+      <c r="F29" s="54" t="s">
         <v>128</v>
       </c>
-      <c r="G29" s="57" t="s">
+      <c r="G29" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="57" t="s">
+      <c r="H29" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="I29" s="57" t="s">
+      <c r="I29" s="54" t="s">
         <v>129</v>
       </c>
-      <c r="J29" s="57" t="s">
+      <c r="J29" s="54" t="s">
         <v>130</v>
       </c>
       <c r="K29" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="L29" s="57" t="s">
+      <c r="L29" s="54" t="s">
         <v>131</v>
       </c>
-      <c r="M29" s="57" t="s">
+      <c r="M29" s="54" t="s">
         <v>132</v>
       </c>
-      <c r="N29" s="57" t="s">
+      <c r="N29" s="54" t="s">
         <v>133</v>
       </c>
-      <c r="O29" s="57" t="s">
+      <c r="O29" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="P29" s="57" t="s">
+      <c r="P29" s="54" t="s">
         <v>134</v>
       </c>
       <c r="Q29" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="R29" s="57" t="s">
+      <c r="R29" s="54" t="s">
         <v>135</v>
       </c>
       <c r="S29" s="29"/>
@@ -5196,49 +5220,49 @@
         <f>B29+1</f>
         <v>8</v>
       </c>
-      <c r="D33" s="57" t="s">
+      <c r="D33" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="E33" s="57" t="s">
+      <c r="E33" s="54" t="s">
         <v>137</v>
       </c>
       <c r="F33" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="G33" s="57" t="s">
+      <c r="G33" s="54" t="s">
         <v>138</v>
       </c>
-      <c r="H33" s="57" t="s">
+      <c r="H33" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="I33" s="57" t="s">
+      <c r="I33" s="54" t="s">
         <v>140</v>
       </c>
       <c r="J33" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="K33" s="57" t="s">
+      <c r="K33" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="L33" s="57" t="s">
+      <c r="L33" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="M33" s="57" t="s">
+      <c r="M33" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="N33" s="57" t="s">
+      <c r="N33" s="54" t="s">
         <v>142</v>
       </c>
       <c r="O33" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="P33" s="57" t="s">
+      <c r="P33" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="Q33" s="57" t="s">
+      <c r="Q33" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="R33" s="57" t="s">
+      <c r="R33" s="54" t="s">
         <v>144</v>
       </c>
       <c r="S33" s="29"/>
@@ -5357,49 +5381,49 @@
         <f>B33+1</f>
         <v>9</v>
       </c>
-      <c r="D37" s="57" t="s">
+      <c r="D37" s="54" t="s">
         <v>145</v>
       </c>
       <c r="E37" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="F37" s="57" t="s">
+      <c r="F37" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="G37" s="57" t="s">
+      <c r="G37" s="54" t="s">
         <v>147</v>
       </c>
-      <c r="H37" s="57" t="s">
+      <c r="H37" s="54" t="s">
         <v>148</v>
       </c>
-      <c r="I37" s="57" t="s">
+      <c r="I37" s="54" t="s">
         <v>149</v>
       </c>
       <c r="J37" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="K37" s="57" t="s">
+      <c r="K37" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="L37" s="57" t="s">
+      <c r="L37" s="54" t="s">
         <v>151</v>
       </c>
-      <c r="M37" s="57" t="s">
+      <c r="M37" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="N37" s="57" t="s">
+      <c r="N37" s="54" t="s">
         <v>153</v>
       </c>
       <c r="O37" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="P37" s="57" t="s">
+      <c r="P37" s="54" t="s">
         <v>154</v>
       </c>
-      <c r="Q37" s="57" t="s">
+      <c r="Q37" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="R37" s="57" t="s">
+      <c r="R37" s="54" t="s">
         <v>107</v>
       </c>
       <c r="S37" s="29"/>
@@ -5520,49 +5544,49 @@
         <f>B37+1</f>
         <v>10</v>
       </c>
-      <c r="D41" s="57" t="s">
+      <c r="D41" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="E41" s="57" t="s">
+      <c r="E41" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="F41" s="57" t="s">
+      <c r="F41" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="G41" s="57" t="s">
+      <c r="G41" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="H41" s="57" t="s">
+      <c r="H41" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="I41" s="57" t="s">
+      <c r="I41" s="54" t="s">
         <v>156</v>
       </c>
       <c r="J41" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="K41" s="57" t="s">
+      <c r="K41" s="54" t="s">
         <v>157</v>
       </c>
-      <c r="L41" s="57" t="s">
+      <c r="L41" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="M41" s="57" t="s">
+      <c r="M41" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="N41" s="57" t="s">
+      <c r="N41" s="54" t="s">
         <v>158</v>
       </c>
-      <c r="O41" s="57" t="s">
+      <c r="O41" s="54" t="s">
         <v>159</v>
       </c>
-      <c r="P41" s="57" t="s">
+      <c r="P41" s="54" t="s">
         <v>160</v>
       </c>
       <c r="Q41" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="R41" s="57" t="s">
+      <c r="R41" s="54" t="s">
         <v>161</v>
       </c>
       <c r="S41" s="29"/>
@@ -5685,49 +5709,49 @@
         <f>B41+1</f>
         <v>11</v>
       </c>
-      <c r="D45" s="57" t="s">
+      <c r="D45" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="E45" s="57" t="s">
+      <c r="E45" s="54" t="s">
         <v>162</v>
       </c>
-      <c r="F45" s="57" t="s">
+      <c r="F45" s="54" t="s">
         <v>99</v>
       </c>
-      <c r="G45" s="57" t="s">
+      <c r="G45" s="54" t="s">
         <v>163</v>
       </c>
-      <c r="H45" s="57" t="s">
+      <c r="H45" s="54" t="s">
         <v>164</v>
       </c>
       <c r="I45" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="J45" s="57" t="s">
+      <c r="J45" s="54" t="s">
         <v>165</v>
       </c>
-      <c r="K45" s="57" t="s">
+      <c r="K45" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="L45" s="57" t="s">
+      <c r="L45" s="54" t="s">
         <v>166</v>
       </c>
-      <c r="M45" s="57" t="s">
+      <c r="M45" s="54" t="s">
         <v>167</v>
       </c>
       <c r="N45" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="O45" s="57" t="s">
+      <c r="O45" s="54" t="s">
         <v>168</v>
       </c>
-      <c r="P45" s="57" t="s">
+      <c r="P45" s="54" t="s">
         <v>169</v>
       </c>
-      <c r="Q45" s="57" t="s">
+      <c r="Q45" s="54" t="s">
         <v>170</v>
       </c>
-      <c r="R45" s="57" t="s">
+      <c r="R45" s="54" t="s">
         <v>45</v>
       </c>
       <c r="S45" s="29"/>
@@ -5851,46 +5875,46 @@
       <c r="D49" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="E49" s="57" t="s">
+      <c r="E49" s="54" t="s">
         <v>171</v>
       </c>
-      <c r="F49" s="57" t="s">
+      <c r="F49" s="54" t="s">
         <v>172</v>
       </c>
-      <c r="G49" s="57" t="s">
+      <c r="G49" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="H49" s="57" t="s">
+      <c r="H49" s="54" t="s">
         <v>154</v>
       </c>
       <c r="I49" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="J49" s="57" t="s">
+      <c r="J49" s="54" t="s">
         <v>173</v>
       </c>
-      <c r="K49" s="57" t="s">
+      <c r="K49" s="54" t="s">
         <v>174</v>
       </c>
-      <c r="L49" s="57" t="s">
+      <c r="L49" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="M49" s="57" t="s">
+      <c r="M49" s="54" t="s">
         <v>175</v>
       </c>
       <c r="N49" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="O49" s="57" t="s">
+      <c r="O49" s="54" t="s">
         <v>176</v>
       </c>
-      <c r="P49" s="57" t="s">
+      <c r="P49" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="Q49" s="57" t="s">
+      <c r="Q49" s="54" t="s">
         <v>177</v>
       </c>
-      <c r="R49" s="57" t="s">
+      <c r="R49" s="54" t="s">
         <v>178</v>
       </c>
       <c r="S49" s="29"/>
@@ -6183,49 +6207,49 @@
         <f>B57+1</f>
         <v>15</v>
       </c>
-      <c r="D61" s="57" t="s">
+      <c r="D61" s="54" t="s">
         <v>180</v>
       </c>
-      <c r="E61" s="57" t="s">
+      <c r="E61" s="54" t="s">
         <v>128</v>
       </c>
-      <c r="F61" s="57" t="s">
+      <c r="F61" s="54" t="s">
         <v>181</v>
       </c>
-      <c r="G61" s="58" t="s">
+      <c r="G61" s="55" t="s">
         <v>182</v>
       </c>
-      <c r="H61" s="57" t="s">
+      <c r="H61" s="54" t="s">
         <v>183</v>
       </c>
-      <c r="I61" s="57" t="s">
+      <c r="I61" s="54" t="s">
         <v>183</v>
       </c>
       <c r="J61" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="K61" s="57" t="s">
+      <c r="K61" s="54" t="s">
         <v>184</v>
       </c>
-      <c r="L61" s="57" t="s">
+      <c r="L61" s="54" t="s">
         <v>185</v>
       </c>
-      <c r="M61" s="57" t="s">
+      <c r="M61" s="54" t="s">
         <v>186</v>
       </c>
-      <c r="N61" s="57" t="s">
+      <c r="N61" s="54" t="s">
         <v>187</v>
       </c>
       <c r="O61" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="P61" s="57" t="s">
+      <c r="P61" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="Q61" s="57" t="s">
+      <c r="Q61" s="54" t="s">
         <v>188</v>
       </c>
-      <c r="R61" s="57" t="s">
+      <c r="R61" s="54" t="s">
         <v>189</v>
       </c>
       <c r="S61" s="29"/>
@@ -6346,49 +6370,49 @@
         <f>B61+1</f>
         <v>16</v>
       </c>
-      <c r="D65" s="57" t="s">
+      <c r="D65" s="54" t="s">
         <v>190</v>
       </c>
       <c r="E65" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="F65" s="57" t="s">
+      <c r="F65" s="54" t="s">
         <v>191</v>
       </c>
-      <c r="G65" s="58" t="s">
+      <c r="G65" s="55" t="s">
         <v>192</v>
       </c>
-      <c r="H65" s="57" t="s">
+      <c r="H65" s="54" t="s">
         <v>193</v>
       </c>
-      <c r="I65" s="57" t="s">
+      <c r="I65" s="54" t="s">
         <v>194</v>
       </c>
       <c r="J65" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="K65" s="57" t="s">
+      <c r="K65" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="L65" s="57" t="s">
+      <c r="L65" s="54" t="s">
         <v>195</v>
       </c>
-      <c r="M65" s="57" t="s">
+      <c r="M65" s="54" t="s">
         <v>196</v>
       </c>
-      <c r="N65" s="57" t="s">
+      <c r="N65" s="54" t="s">
         <v>197</v>
       </c>
       <c r="O65" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="P65" s="57" t="s">
+      <c r="P65" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="Q65" s="57" t="s">
+      <c r="Q65" s="54" t="s">
         <v>198</v>
       </c>
-      <c r="R65" s="57" t="s">
+      <c r="R65" s="54" t="s">
         <v>199</v>
       </c>
       <c r="S65" s="29"/>
@@ -6507,49 +6531,49 @@
         <f>B65+1</f>
         <v>17</v>
       </c>
-      <c r="D69" s="57" t="s">
+      <c r="D69" s="54" t="s">
         <v>200</v>
       </c>
       <c r="E69" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="F69" s="57" t="s">
+      <c r="F69" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="G69" s="58" t="s">
+      <c r="G69" s="55" t="s">
         <v>202</v>
       </c>
-      <c r="H69" s="57" t="s">
+      <c r="H69" s="54" t="s">
         <v>186</v>
       </c>
-      <c r="I69" s="57" t="s">
+      <c r="I69" s="54" t="s">
         <v>203</v>
       </c>
       <c r="J69" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="K69" s="57" t="s">
+      <c r="K69" s="54" t="s">
         <v>204</v>
       </c>
-      <c r="L69" s="57" t="s">
+      <c r="L69" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="M69" s="57" t="s">
+      <c r="M69" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="N69" s="57" t="s">
+      <c r="N69" s="54" t="s">
         <v>207</v>
       </c>
       <c r="O69" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="P69" s="57" t="s">
+      <c r="P69" s="54" t="s">
         <v>208</v>
       </c>
-      <c r="Q69" s="57" t="s">
+      <c r="Q69" s="54" t="s">
         <v>209</v>
       </c>
-      <c r="R69" s="57" t="s">
+      <c r="R69" s="54" t="s">
         <v>210</v>
       </c>
       <c r="S69" s="29"/>
@@ -6668,49 +6692,49 @@
         <f>B69+1</f>
         <v>18</v>
       </c>
-      <c r="D73" s="57" t="s">
+      <c r="D73" s="54" t="s">
         <v>210</v>
       </c>
       <c r="E73" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="F73" s="57" t="s">
+      <c r="F73" s="54" t="s">
         <v>211</v>
       </c>
-      <c r="G73" s="57" t="s">
+      <c r="G73" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="H73" s="57" t="s">
+      <c r="H73" s="54" t="s">
         <v>213</v>
       </c>
-      <c r="I73" s="57" t="s">
+      <c r="I73" s="54" t="s">
         <v>214</v>
       </c>
       <c r="J73" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="K73" s="57" t="s">
+      <c r="K73" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="L73" s="57" t="s">
+      <c r="L73" s="54" t="s">
         <v>216</v>
       </c>
-      <c r="M73" s="57" t="s">
+      <c r="M73" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="N73" s="57" t="s">
+      <c r="N73" s="54" t="s">
         <v>156</v>
       </c>
       <c r="O73" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="P73" s="57" t="s">
+      <c r="P73" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="Q73" s="57" t="s">
+      <c r="Q73" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="R73" s="57" t="s">
+      <c r="R73" s="54" t="s">
         <v>217</v>
       </c>
       <c r="S73" s="29"/>
@@ -6829,49 +6853,49 @@
         <f>B73+1</f>
         <v>19</v>
       </c>
-      <c r="D77" s="57" t="s">
+      <c r="D77" s="54" t="s">
         <v>218</v>
       </c>
-      <c r="E77" s="57" t="s">
+      <c r="E77" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="F77" s="57" t="s">
+      <c r="F77" s="54" t="s">
         <v>220</v>
       </c>
       <c r="G77" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="H77" s="57" t="s">
+      <c r="H77" s="54" t="s">
         <v>221</v>
       </c>
-      <c r="I77" s="57" t="s">
+      <c r="I77" s="54" t="s">
         <v>222</v>
       </c>
-      <c r="J77" s="57" t="s">
+      <c r="J77" s="54" t="s">
         <v>223</v>
       </c>
-      <c r="K77" s="57" t="s">
+      <c r="K77" s="54" t="s">
         <v>224</v>
       </c>
       <c r="L77" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="M77" s="57" t="s">
+      <c r="M77" s="54" t="s">
         <v>225</v>
       </c>
-      <c r="N77" s="57" t="s">
+      <c r="N77" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="O77" s="57" t="s">
+      <c r="O77" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="P77" s="57" t="s">
+      <c r="P77" s="54" t="s">
         <v>161</v>
       </c>
       <c r="Q77" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="R77" s="57" t="s">
+      <c r="R77" s="54" t="s">
         <v>30</v>
       </c>
       <c r="S77" s="29"/>
@@ -6976,19 +7000,19 @@
         <f>B77+1</f>
         <v>20</v>
       </c>
-      <c r="D81" s="57" t="s">
+      <c r="D81" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="E81" s="57" t="s">
+      <c r="E81" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="F81" s="57" t="s">
+      <c r="F81" s="54" t="s">
         <v>229</v>
       </c>
-      <c r="G81" s="57" t="s">
+      <c r="G81" s="54" t="s">
         <v>230</v>
       </c>
-      <c r="H81" s="57" t="s">
+      <c r="H81" s="54" t="s">
         <v>160</v>
       </c>
       <c r="I81" s="51" t="s">
@@ -7194,49 +7218,49 @@
         <f>B85+1</f>
         <v>22</v>
       </c>
-      <c r="D89" s="57" t="s">
+      <c r="D89" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="E89" s="57" t="s">
+      <c r="E89" s="54" t="s">
         <v>180</v>
       </c>
-      <c r="F89" s="57" t="s">
+      <c r="F89" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="G89" s="57" t="s">
+      <c r="G89" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="H89" s="57" t="s">
+      <c r="H89" s="54" t="s">
         <v>231</v>
       </c>
-      <c r="I89" s="57" t="s">
+      <c r="I89" s="54" t="s">
         <v>43</v>
       </c>
       <c r="J89" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="K89" s="57" t="s">
+      <c r="K89" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="L89" s="57" t="s">
+      <c r="L89" s="54" t="s">
         <v>233</v>
       </c>
-      <c r="M89" s="57" t="s">
+      <c r="M89" s="54" t="s">
         <v>186</v>
       </c>
-      <c r="N89" s="57" t="s">
+      <c r="N89" s="54" t="s">
         <v>234</v>
       </c>
       <c r="O89" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="P89" s="57" t="s">
+      <c r="P89" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="Q89" s="57" t="s">
+      <c r="Q89" s="54" t="s">
         <v>235</v>
       </c>
-      <c r="R89" s="57" t="s">
+      <c r="R89" s="54" t="s">
         <v>236</v>
       </c>
       <c r="S89" s="29"/>
@@ -7357,49 +7381,49 @@
         <f>B89+1</f>
         <v>23</v>
       </c>
-      <c r="D93" s="57" t="s">
+      <c r="D93" s="54" t="s">
         <v>237</v>
       </c>
       <c r="E93" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="F93" s="57" t="s">
+      <c r="F93" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="G93" s="57" t="s">
+      <c r="G93" s="54" t="s">
         <v>238</v>
       </c>
-      <c r="H93" s="57" t="s">
+      <c r="H93" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="I93" s="57" t="s">
+      <c r="I93" s="54" t="s">
         <v>239</v>
       </c>
       <c r="J93" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="K93" s="57" t="s">
+      <c r="K93" s="54" t="s">
         <v>240</v>
       </c>
-      <c r="L93" s="57" t="s">
+      <c r="L93" s="54" t="s">
         <v>241</v>
       </c>
-      <c r="M93" s="57" t="s">
+      <c r="M93" s="54" t="s">
         <v>242</v>
       </c>
-      <c r="N93" s="57" t="s">
+      <c r="N93" s="54" t="s">
         <v>243</v>
       </c>
       <c r="O93" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="P93" s="57" t="s">
+      <c r="P93" s="54" t="s">
         <v>244</v>
       </c>
-      <c r="Q93" s="57" t="s">
+      <c r="Q93" s="54" t="s">
         <v>245</v>
       </c>
-      <c r="R93" s="57" t="s">
+      <c r="R93" s="54" t="s">
         <v>246</v>
       </c>
       <c r="S93" s="29"/>
@@ -7518,49 +7542,49 @@
         <f>B93+1</f>
         <v>24</v>
       </c>
-      <c r="D97" s="57" t="s">
+      <c r="D97" s="54" t="s">
         <v>247</v>
       </c>
       <c r="E97" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="F97" s="57" t="s">
+      <c r="F97" s="54" t="s">
         <v>248</v>
       </c>
-      <c r="G97" s="58" t="s">
+      <c r="G97" s="55" t="s">
         <v>249</v>
       </c>
-      <c r="H97" s="57" t="s">
+      <c r="H97" s="54" t="s">
         <v>250</v>
       </c>
-      <c r="I97" s="57" t="s">
+      <c r="I97" s="54" t="s">
         <v>251</v>
       </c>
       <c r="J97" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="K97" s="57" t="s">
+      <c r="K97" s="54" t="s">
         <v>252</v>
       </c>
-      <c r="L97" s="57" t="s">
+      <c r="L97" s="54" t="s">
         <v>252</v>
       </c>
-      <c r="M97" s="57" t="s">
+      <c r="M97" s="54" t="s">
         <v>253</v>
       </c>
-      <c r="N97" s="57" t="s">
+      <c r="N97" s="54" t="s">
         <v>253</v>
       </c>
       <c r="O97" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="P97" s="57" t="s">
+      <c r="P97" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="Q97" s="57" t="s">
+      <c r="Q97" s="54" t="s">
         <v>254</v>
       </c>
-      <c r="R97" s="57" t="s">
+      <c r="R97" s="54" t="s">
         <v>139</v>
       </c>
       <c r="S97" s="29"/>
@@ -7679,49 +7703,49 @@
         <f>B97+1</f>
         <v>25</v>
       </c>
-      <c r="D101" s="57" t="s">
+      <c r="D101" s="54" t="s">
         <v>255</v>
       </c>
-      <c r="E101" s="57" t="s">
+      <c r="E101" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="F101" s="57" t="s">
+      <c r="F101" s="54" t="s">
         <v>194</v>
       </c>
       <c r="G101" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="H101" s="57" t="s">
+      <c r="H101" s="54" t="s">
         <v>256</v>
       </c>
-      <c r="I101" s="57" t="s">
+      <c r="I101" s="54" t="s">
         <v>185</v>
       </c>
-      <c r="J101" s="57" t="s">
+      <c r="J101" s="54" t="s">
         <v>153</v>
       </c>
-      <c r="K101" s="57" t="s">
+      <c r="K101" s="54" t="s">
         <v>257</v>
       </c>
       <c r="L101" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="M101" s="57" t="s">
+      <c r="M101" s="54" t="s">
         <v>258</v>
       </c>
-      <c r="N101" s="57" t="s">
+      <c r="N101" s="54" t="s">
         <v>237</v>
       </c>
-      <c r="O101" s="57" t="s">
+      <c r="O101" s="54" t="s">
         <v>259</v>
       </c>
-      <c r="P101" s="57" t="s">
+      <c r="P101" s="54" t="s">
         <v>260</v>
       </c>
       <c r="Q101" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="R101" s="57" t="s">
+      <c r="R101" s="54" t="s">
         <v>261</v>
       </c>
       <c r="S101" s="29"/>
@@ -7840,49 +7864,49 @@
         <f>B101+1</f>
         <v>26</v>
       </c>
-      <c r="D105" s="57" t="s">
+      <c r="D105" s="54" t="s">
         <v>262</v>
       </c>
-      <c r="E105" s="57" t="s">
+      <c r="E105" s="54" t="s">
         <v>263</v>
       </c>
-      <c r="F105" s="57" t="s">
+      <c r="F105" s="54" t="s">
         <v>264</v>
       </c>
       <c r="G105" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="H105" s="57" t="s">
+      <c r="H105" s="54" t="s">
         <v>265</v>
       </c>
-      <c r="I105" s="57" t="s">
+      <c r="I105" s="54" t="s">
         <v>266</v>
       </c>
-      <c r="J105" s="57" t="s">
+      <c r="J105" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="K105" s="57" t="s">
+      <c r="K105" s="54" t="s">
         <v>268</v>
       </c>
       <c r="L105" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="M105" s="57" t="s">
+      <c r="M105" s="54" t="s">
         <v>154</v>
       </c>
-      <c r="N105" s="57" t="s">
+      <c r="N105" s="54" t="s">
         <v>269</v>
       </c>
-      <c r="O105" s="59" t="s">
+      <c r="O105" s="56" t="s">
         <v>270</v>
       </c>
-      <c r="P105" s="57" t="s">
+      <c r="P105" s="54" t="s">
         <v>42</v>
       </c>
       <c r="Q105" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="R105" s="57" t="s">
+      <c r="R105" s="54" t="s">
         <v>215</v>
       </c>
       <c r="S105" s="29"/>
@@ -8003,49 +8027,49 @@
         <f>B105+1</f>
         <v>27</v>
       </c>
-      <c r="D109" s="57" t="s">
+      <c r="D109" s="54" t="s">
         <v>216</v>
       </c>
-      <c r="E109" s="57" t="s">
+      <c r="E109" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="F109" s="57" t="s">
+      <c r="F109" s="54" t="s">
         <v>156</v>
       </c>
       <c r="G109" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="H109" s="57" t="s">
+      <c r="H109" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="I109" s="57" t="s">
+      <c r="I109" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="J109" s="57" t="s">
+      <c r="J109" s="54" t="s">
         <v>271</v>
       </c>
-      <c r="K109" s="57" t="s">
+      <c r="K109" s="54" t="s">
         <v>272</v>
       </c>
-      <c r="L109" s="57" t="s">
+      <c r="L109" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="M109" s="57" t="s">
+      <c r="M109" s="54" t="s">
         <v>274</v>
       </c>
       <c r="N109" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="O109" s="57" t="s">
+      <c r="O109" s="54" t="s">
         <v>275</v>
       </c>
-      <c r="P109" s="57" t="s">
+      <c r="P109" s="54" t="s">
         <v>276</v>
       </c>
-      <c r="Q109" s="57" t="s">
+      <c r="Q109" s="54" t="s">
         <v>277</v>
       </c>
-      <c r="R109" s="57" t="s">
+      <c r="R109" s="54" t="s">
         <v>278</v>
       </c>
       <c r="S109" s="29"/>
@@ -8165,37 +8189,37 @@
       <c r="D113" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="E113" s="57" t="s">
+      <c r="E113" s="54" t="s">
         <v>279</v>
       </c>
-      <c r="F113" s="57" t="s">
+      <c r="F113" s="54" t="s">
         <v>280</v>
       </c>
-      <c r="G113" s="57" t="s">
+      <c r="G113" s="54" t="s">
         <v>281</v>
       </c>
-      <c r="H113" s="57" t="s">
+      <c r="H113" s="54" t="s">
         <v>188</v>
       </c>
       <c r="I113" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="J113" s="57" t="s">
+      <c r="J113" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="K113" s="57" t="s">
+      <c r="K113" s="54" t="s">
         <v>282</v>
       </c>
-      <c r="L113" s="57" t="s">
+      <c r="L113" s="54" t="s">
         <v>283</v>
       </c>
-      <c r="M113" s="57" t="s">
+      <c r="M113" s="54" t="s">
         <v>283</v>
       </c>
-      <c r="N113" s="57" t="s">
+      <c r="N113" s="54" t="s">
         <v>230</v>
       </c>
-      <c r="O113" s="59" t="s">
+      <c r="O113" s="56" t="s">
         <v>160</v>
       </c>
       <c r="P113" s="51" t="s">
@@ -8404,49 +8428,49 @@
         <f>B117+1</f>
         <v>30</v>
       </c>
-      <c r="D121" s="57" t="s">
+      <c r="D121" s="54" t="s">
         <v>284</v>
       </c>
-      <c r="E121" s="57" t="s">
+      <c r="E121" s="54" t="s">
         <v>128</v>
       </c>
       <c r="F121" s="51" t="s">
         <v>285</v>
       </c>
-      <c r="G121" s="58" t="s">
+      <c r="G121" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="H121" s="57" t="s">
+      <c r="H121" s="54" t="s">
         <v>286</v>
       </c>
-      <c r="I121" s="57" t="s">
+      <c r="I121" s="54" t="s">
         <v>287</v>
       </c>
-      <c r="J121" s="57" t="s">
+      <c r="J121" s="54" t="s">
         <v>288</v>
       </c>
-      <c r="K121" s="57" t="s">
+      <c r="K121" s="54" t="s">
         <v>289</v>
       </c>
-      <c r="L121" s="57" t="s">
+      <c r="L121" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="M121" s="57" t="s">
+      <c r="M121" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="N121" s="57" t="s">
+      <c r="N121" s="54" t="s">
         <v>271</v>
       </c>
       <c r="O121" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="P121" s="57" t="s">
+      <c r="P121" s="54" t="s">
         <v>254</v>
       </c>
-      <c r="Q121" s="57" t="s">
+      <c r="Q121" s="54" t="s">
         <v>177</v>
       </c>
-      <c r="R121" s="57" t="s">
+      <c r="R121" s="54" t="s">
         <v>290</v>
       </c>
       <c r="S121" s="29"/>
@@ -8567,49 +8591,49 @@
         <f>B121+1</f>
         <v>31</v>
       </c>
-      <c r="D125" s="57" t="s">
+      <c r="D125" s="54" t="s">
         <v>230</v>
       </c>
-      <c r="E125" s="57" t="s">
+      <c r="E125" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="F125" s="57" t="s">
+      <c r="F125" s="54" t="s">
         <v>291</v>
       </c>
       <c r="G125" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="H125" s="57" t="s">
+      <c r="H125" s="54" t="s">
         <v>270</v>
       </c>
-      <c r="I125" s="57" t="s">
+      <c r="I125" s="54" t="s">
         <v>292</v>
       </c>
       <c r="J125" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="K125" s="57" t="s">
+      <c r="K125" s="54" t="s">
         <v>186</v>
       </c>
-      <c r="L125" s="57" t="s">
+      <c r="L125" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="M125" s="57" t="s">
+      <c r="M125" s="54" t="s">
         <v>174</v>
       </c>
-      <c r="N125" s="57" t="s">
+      <c r="N125" s="54" t="s">
         <v>282</v>
       </c>
       <c r="O125" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="P125" s="57" t="s">
+      <c r="P125" s="54" t="s">
         <v>186</v>
       </c>
-      <c r="Q125" s="57" t="s">
+      <c r="Q125" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="R125" s="57" t="s">
+      <c r="R125" s="54" t="s">
         <v>293</v>
       </c>
       <c r="S125" s="29"/>
@@ -8728,49 +8752,49 @@
         <f>B125+1</f>
         <v>32</v>
       </c>
-      <c r="D129" s="57" t="s">
+      <c r="D129" s="54" t="s">
         <v>229</v>
       </c>
       <c r="E129" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="F129" s="57" t="s">
+      <c r="F129" s="54" t="s">
         <v>294</v>
       </c>
-      <c r="G129" s="57" t="s">
+      <c r="G129" s="54" t="s">
         <v>295</v>
       </c>
-      <c r="H129" s="57" t="s">
+      <c r="H129" s="54" t="s">
         <v>296</v>
       </c>
-      <c r="I129" s="57" t="s">
+      <c r="I129" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="J129" s="57" t="s">
+      <c r="J129" s="54" t="s">
         <v>33</v>
       </c>
       <c r="K129" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="L129" s="60" t="s">
+      <c r="L129" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="M129" s="57" t="s">
+      <c r="M129" s="54" t="s">
         <v>221</v>
       </c>
-      <c r="N129" s="57" t="s">
+      <c r="N129" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="O129" s="57" t="s">
+      <c r="O129" s="54" t="s">
         <v>297</v>
       </c>
       <c r="P129" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="Q129" s="57" t="s">
+      <c r="Q129" s="54" t="s">
         <v>298</v>
       </c>
-      <c r="R129" s="57" t="s">
+      <c r="R129" s="54" t="s">
         <v>140</v>
       </c>
       <c r="S129" s="29"/>
@@ -8889,49 +8913,49 @@
         <f>B129+1</f>
         <v>33</v>
       </c>
-      <c r="D133" s="57" t="s">
+      <c r="D133" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="E133" s="57" t="s">
+      <c r="E133" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="F133" s="57" t="s">
+      <c r="F133" s="54" t="s">
         <v>136</v>
       </c>
       <c r="G133" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="H133" s="57" t="s">
+      <c r="H133" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="I133" s="57" t="s">
+      <c r="I133" s="54" t="s">
         <v>221</v>
       </c>
-      <c r="J133" s="57" t="s">
+      <c r="J133" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="K133" s="57" t="s">
+      <c r="K133" s="54" t="s">
         <v>299</v>
       </c>
       <c r="L133" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="M133" s="57" t="s">
+      <c r="M133" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="N133" s="57" t="s">
+      <c r="N133" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="O133" s="57" t="s">
+      <c r="O133" s="54" t="s">
         <v>301</v>
       </c>
-      <c r="P133" s="57" t="s">
+      <c r="P133" s="54" t="s">
         <v>221</v>
       </c>
       <c r="Q133" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="R133" s="57" t="s">
+      <c r="R133" s="54" t="s">
         <v>302</v>
       </c>
       <c r="S133" s="29"/>
@@ -9050,46 +9074,46 @@
         <f>B133+1</f>
         <v>34</v>
       </c>
-      <c r="D137" s="57" t="s">
+      <c r="D137" s="54" t="s">
         <v>301</v>
       </c>
-      <c r="E137" s="57" t="s">
+      <c r="E137" s="54" t="s">
         <v>221</v>
       </c>
       <c r="F137" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="G137" s="57" t="s">
+      <c r="G137" s="54" t="s">
         <v>161</v>
       </c>
-      <c r="H137" s="57" t="s">
+      <c r="H137" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="I137" s="57" t="s">
+      <c r="I137" s="54" t="s">
         <v>270</v>
       </c>
-      <c r="J137" s="57" t="s">
+      <c r="J137" s="54" t="s">
         <v>303</v>
       </c>
-      <c r="K137" s="57" t="s">
+      <c r="K137" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="L137" s="57" t="s">
+      <c r="L137" s="54" t="s">
         <v>269</v>
       </c>
-      <c r="M137" s="57" t="s">
+      <c r="M137" s="54" t="s">
         <v>304</v>
       </c>
       <c r="N137" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="O137" s="57" t="s">
+      <c r="O137" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="P137" s="57" t="s">
+      <c r="P137" s="54" t="s">
         <v>305</v>
       </c>
-      <c r="Q137" s="57" t="s">
+      <c r="Q137" s="54" t="s">
         <v>306</v>
       </c>
       <c r="R137" s="51" t="s">
@@ -9216,46 +9240,46 @@
       <c r="D141" s="51" t="s">
         <v>308</v>
       </c>
-      <c r="E141" s="57" t="s">
+      <c r="E141" s="54" t="s">
         <v>309</v>
       </c>
-      <c r="F141" s="57" t="s">
+      <c r="F141" s="54" t="s">
         <v>236</v>
       </c>
-      <c r="G141" s="58" t="s">
+      <c r="G141" s="55" t="s">
         <v>235</v>
       </c>
-      <c r="H141" s="57" t="s">
+      <c r="H141" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="I141" s="57" t="s">
+      <c r="I141" s="54" t="s">
         <v>221</v>
       </c>
-      <c r="J141" s="57" t="s">
+      <c r="J141" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="K141" s="57" t="s">
+      <c r="K141" s="54" t="s">
         <v>221</v>
       </c>
       <c r="L141" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="M141" s="57" t="s">
+      <c r="M141" s="54" t="s">
         <v>310</v>
       </c>
-      <c r="N141" s="57" t="s">
+      <c r="N141" s="54" t="s">
         <v>236</v>
       </c>
-      <c r="O141" s="57" t="s">
+      <c r="O141" s="54" t="s">
         <v>235</v>
       </c>
-      <c r="P141" s="57" t="s">
+      <c r="P141" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="Q141" s="57" t="s">
+      <c r="Q141" s="54" t="s">
         <v>269</v>
       </c>
-      <c r="R141" s="57" t="s">
+      <c r="R141" s="54" t="s">
         <v>228</v>
       </c>
       <c r="S141" s="29"/>
@@ -9372,46 +9396,46 @@
         <f>B141+1</f>
         <v>36</v>
       </c>
-      <c r="D145" s="57" t="s">
+      <c r="D145" s="54" t="s">
         <v>269</v>
       </c>
       <c r="E145" s="51" t="s">
         <v>311</v>
       </c>
-      <c r="F145" s="57" t="s">
+      <c r="F145" s="54" t="s">
         <v>312</v>
       </c>
       <c r="G145" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="H145" s="57" t="s">
+      <c r="H145" s="54" t="s">
         <v>313</v>
       </c>
       <c r="I145" s="51" t="s">
         <v>285</v>
       </c>
-      <c r="J145" s="57" t="s">
+      <c r="J145" s="54" t="s">
         <v>314</v>
       </c>
-      <c r="K145" s="57" t="s">
+      <c r="K145" s="54" t="s">
         <v>216</v>
       </c>
-      <c r="L145" s="57" t="s">
+      <c r="L145" s="54" t="s">
         <v>45</v>
       </c>
       <c r="M145" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="N145" s="57" t="s">
+      <c r="N145" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="O145" s="57" t="s">
+      <c r="O145" s="54" t="s">
         <v>316</v>
       </c>
-      <c r="P145" s="57" t="s">
+      <c r="P145" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="Q145" s="57" t="s">
+      <c r="Q145" s="54" t="s">
         <v>317</v>
       </c>
       <c r="R145" s="51" t="s">

--- a/output7/【河洛文讀注音-雅俗通】《岳陽樓記》.xlsx
+++ b/output7/【河洛文讀注音-雅俗通】《岳陽樓記》.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272C89F4-6D53-41A2-AD77-131F3C8E2469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A51153F-C5FF-4463-9DBC-7AFA2CFBED62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
     <sheet name="漢字注音" sheetId="9" r:id="rId2"/>
-    <sheet name="缺字表" sheetId="109" r:id="rId3"/>
-    <sheet name="人工標音字庫" sheetId="108" r:id="rId4"/>
-    <sheet name="標音字庫" sheetId="107" r:id="rId5"/>
+    <sheet name="缺字表" sheetId="112" r:id="rId3"/>
+    <sheet name="人工標音字庫" sheetId="111" r:id="rId4"/>
+    <sheet name="標音字庫" sheetId="110" r:id="rId5"/>
     <sheet name="缺字表 (範例)" sheetId="100" r:id="rId6"/>
     <sheet name="漢字庫（範例）" sheetId="10" r:id="rId7"/>
   </sheets>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="931">
   <si>
     <t>Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1067,9 +1067,6 @@
     <t>khing3</t>
   </si>
   <si>
-    <t>lah8</t>
-  </si>
-  <si>
     <t>lian5</t>
   </si>
   <si>
@@ -1082,9 +1079,6 @@
     <t>zu2</t>
   </si>
   <si>
-    <t>kiann1</t>
-  </si>
-  <si>
     <t>tik4</t>
   </si>
   <si>
@@ -1139,18 +1133,12 @@
     <t>zing1</t>
   </si>
   <si>
-    <t>ku7</t>
-  </si>
-  <si>
     <t>ze3</t>
   </si>
   <si>
     <t>khik4</t>
   </si>
   <si>
-    <t>tng5</t>
-  </si>
-  <si>
     <t>hian5</t>
   </si>
   <si>
@@ -1620,622 +1608,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>經三去</t>
-  </si>
-  <si>
-    <t>膠八柳</t>
-  </si>
-  <si>
-    <t>艍三時</t>
-  </si>
-  <si>
-    <t>堅五柳</t>
-  </si>
-  <si>
-    <t>君一出</t>
-  </si>
-  <si>
-    <t>經五地</t>
-  </si>
-  <si>
-    <t>艍二曾</t>
-  </si>
-  <si>
-    <t>驚一求</t>
-  </si>
-  <si>
-    <t>經四地</t>
-  </si>
-  <si>
-    <t>丩二時</t>
-  </si>
-  <si>
-    <t>膠一邊</t>
-  </si>
-  <si>
-    <t>經五柳</t>
-  </si>
-  <si>
-    <t>君七求</t>
-  </si>
-  <si>
-    <t>觀八英</t>
-  </si>
-  <si>
-    <t>經五門</t>
-  </si>
-  <si>
-    <t>經三曾</t>
-  </si>
-  <si>
-    <t>公一他</t>
-  </si>
-  <si>
-    <t>巾五入</t>
-  </si>
-  <si>
-    <t>高五喜</t>
-  </si>
-  <si>
-    <t>經四邊</t>
-  </si>
-  <si>
-    <t>檜三喜</t>
-  </si>
-  <si>
-    <t>艍七去</t>
-  </si>
-  <si>
-    <t>經一喜</t>
-  </si>
-  <si>
-    <t>皆二耐</t>
-  </si>
-  <si>
-    <t>恭七地</t>
-  </si>
-  <si>
-    <t>丩一時</t>
-  </si>
-  <si>
-    <t>江八語</t>
-  </si>
-  <si>
-    <t>姜五英</t>
-  </si>
-  <si>
-    <t>交五柳</t>
-  </si>
-  <si>
-    <t>經一曾</t>
-  </si>
-  <si>
-    <t>居五求</t>
-  </si>
-  <si>
-    <t>艍七求</t>
-  </si>
-  <si>
-    <t>伽三曾</t>
-  </si>
-  <si>
-    <t>經四去</t>
-  </si>
-  <si>
-    <t>鋼五地</t>
-  </si>
-  <si>
-    <t>堅五喜</t>
-  </si>
-  <si>
-    <t>金一求</t>
-  </si>
-  <si>
-    <t>居一時</t>
-  </si>
-  <si>
-    <t>艍三喜</t>
-  </si>
-  <si>
-    <t>艍一英</t>
-  </si>
-  <si>
-    <t>恭七時</t>
-  </si>
-  <si>
-    <t>恭八時</t>
-  </si>
-  <si>
-    <t>艍二英</t>
-  </si>
-  <si>
-    <t>公四曾</t>
-  </si>
-  <si>
-    <t>君五門</t>
-  </si>
-  <si>
-    <t>居二英</t>
-  </si>
-  <si>
-    <t>居三求</t>
-  </si>
-  <si>
-    <t>居一曾</t>
-  </si>
-  <si>
-    <t>觀一求</t>
-  </si>
-  <si>
-    <t>艍一喜</t>
-  </si>
-  <si>
-    <t>經三時</t>
-  </si>
-  <si>
-    <t>公七曾</t>
-  </si>
-  <si>
-    <t>皆七曾</t>
-  </si>
-  <si>
-    <t>公七地</t>
-  </si>
-  <si>
-    <t>驚五地</t>
-  </si>
-  <si>
-    <t>巾四英</t>
-  </si>
-  <si>
-    <t>沽五英</t>
-  </si>
-  <si>
-    <t>觀二英</t>
-  </si>
-  <si>
-    <t>干一時</t>
-  </si>
-  <si>
-    <t>君一他</t>
-  </si>
-  <si>
-    <t>恭五地</t>
-  </si>
-  <si>
-    <t>江一求</t>
-  </si>
-  <si>
-    <t>高七喜</t>
-  </si>
-  <si>
-    <t>經五喜</t>
-  </si>
-  <si>
-    <t>艍五門</t>
-  </si>
-  <si>
-    <t>皆五語</t>
-  </si>
-  <si>
-    <t>嬌一地</t>
-  </si>
-  <si>
-    <t>經八時</t>
-  </si>
-  <si>
-    <t>兼一英</t>
-  </si>
-  <si>
-    <t>居三去</t>
-  </si>
-  <si>
-    <t>干七門</t>
-  </si>
-  <si>
-    <t>堅一出</t>
-  </si>
-  <si>
-    <t>艍二出</t>
-  </si>
-  <si>
-    <t>經四曾</t>
-  </si>
-  <si>
-    <t>皆七地</t>
-  </si>
-  <si>
-    <t>迦七英</t>
-  </si>
-  <si>
-    <t>堅五曾</t>
-  </si>
-  <si>
-    <t>君八時</t>
-  </si>
-  <si>
-    <t>居七邊</t>
-  </si>
-  <si>
-    <t>堅五入</t>
-  </si>
-  <si>
-    <t>公四邊</t>
-  </si>
-  <si>
-    <t>兼四求</t>
-  </si>
-  <si>
-    <t>甘五柳</t>
-  </si>
-  <si>
-    <t>經八求</t>
-  </si>
-  <si>
-    <t>嬌一時</t>
-  </si>
-  <si>
-    <t>姜一時</t>
-  </si>
-  <si>
-    <t>嘉四去</t>
-  </si>
-  <si>
-    <t>高一時</t>
-  </si>
-  <si>
-    <t>高一地</t>
-  </si>
-  <si>
-    <t>檜七喜</t>
-  </si>
-  <si>
-    <t>甘二柳</t>
-  </si>
-  <si>
-    <t>君八門</t>
-  </si>
-  <si>
-    <t>經五曾</t>
-  </si>
-  <si>
-    <t>居七英</t>
-  </si>
-  <si>
-    <t>沽五喜</t>
-  </si>
-  <si>
-    <t>恭八入</t>
-  </si>
-  <si>
     <t>規一喜</t>
-  </si>
-  <si>
-    <t>兼五柳</t>
-  </si>
-  <si>
-    <t>檜八語</t>
-  </si>
-  <si>
-    <t>君四邊</t>
-  </si>
-  <si>
-    <t>規一去</t>
-  </si>
-  <si>
-    <t>公一喜</t>
-  </si>
-  <si>
-    <t>沽七耐</t>
-  </si>
-  <si>
-    <t>江八地</t>
-  </si>
-  <si>
-    <t>公七柳</t>
-  </si>
-  <si>
-    <t>皆五邊</t>
-  </si>
-  <si>
-    <t>公一去</t>
-  </si>
-  <si>
-    <t>巾八入</t>
-  </si>
-  <si>
-    <t>經一時</t>
-  </si>
-  <si>
-    <t>君二英</t>
-  </si>
-  <si>
-    <t>嬌七英</t>
-  </si>
-  <si>
-    <t>兼五曾</t>
-  </si>
-  <si>
-    <t>居二柳</t>
-  </si>
-  <si>
-    <t>江五喜</t>
-  </si>
-  <si>
-    <t>經一去</t>
-  </si>
-  <si>
-    <t>金四出</t>
-  </si>
-  <si>
-    <t>規一出</t>
-  </si>
-  <si>
-    <t>公八邊</t>
-  </si>
-  <si>
-    <t>沽七門</t>
-  </si>
-  <si>
-    <t>沽二喜</t>
-  </si>
-  <si>
-    <t>嬌三時</t>
-  </si>
-  <si>
-    <t>觀五英</t>
-  </si>
-  <si>
-    <t>伽五他</t>
-  </si>
-  <si>
-    <t>經一地</t>
-  </si>
-  <si>
-    <t>艍一時</t>
-  </si>
-  <si>
-    <t>丩二英</t>
-  </si>
-  <si>
-    <t>艍二去</t>
-  </si>
-  <si>
-    <t>公四求</t>
-  </si>
-  <si>
-    <t>乖五喜</t>
-  </si>
-  <si>
-    <t>姜一喜</t>
-  </si>
-  <si>
-    <t>丩一英</t>
-  </si>
-  <si>
-    <t>規三英</t>
-  </si>
-  <si>
-    <t>居一求</t>
-  </si>
-  <si>
-    <t>觀二門</t>
-  </si>
-  <si>
-    <t>公八門</t>
-  </si>
-  <si>
-    <t>甘二求</t>
-  </si>
-  <si>
-    <t>居五入</t>
-  </si>
-  <si>
-    <t>居一邊</t>
-  </si>
-  <si>
-    <t>迦二曾</t>
-  </si>
-  <si>
-    <t>居三曾</t>
-  </si>
-  <si>
-    <t>經二求</t>
-  </si>
-  <si>
-    <t>高一頗</t>
-  </si>
-  <si>
-    <t>干五柳</t>
-  </si>
-  <si>
-    <t>經一求</t>
-  </si>
-  <si>
-    <t>膠七喜</t>
-  </si>
-  <si>
-    <t>堅一他</t>
-  </si>
-  <si>
-    <t>公一求</t>
-  </si>
-  <si>
-    <t>經四頗</t>
-  </si>
-  <si>
-    <t>經二去</t>
-  </si>
-  <si>
-    <t>膠一時</t>
-  </si>
-  <si>
-    <t>茄一英</t>
-  </si>
-  <si>
-    <t>姜五時</t>
-  </si>
-  <si>
-    <t>金八曾</t>
-  </si>
-  <si>
-    <t>金二求</t>
-  </si>
-  <si>
-    <t>丩五英</t>
-  </si>
-  <si>
-    <t>經二英</t>
-  </si>
-  <si>
-    <t>干七語</t>
-  </si>
-  <si>
-    <t>居二曾</t>
-  </si>
-  <si>
-    <t>更一出</t>
-  </si>
-  <si>
-    <t>經八喜</t>
-  </si>
-  <si>
-    <t>堅一英</t>
-  </si>
-  <si>
-    <t>艍五頗</t>
-  </si>
-  <si>
-    <t>姜八英</t>
-  </si>
-  <si>
-    <t>經七曾</t>
-  </si>
-  <si>
-    <t>兼五地</t>
-  </si>
-  <si>
-    <t>艍五語</t>
-  </si>
-  <si>
-    <t>瓜一求</t>
-  </si>
-  <si>
-    <t>沽七喜</t>
-  </si>
-  <si>
-    <t>膠四地</t>
-  </si>
-  <si>
-    <t>交七雅</t>
-  </si>
-  <si>
-    <t>金一時</t>
-  </si>
-  <si>
-    <t>公三去</t>
-  </si>
-  <si>
-    <t>巾五時</t>
-  </si>
-  <si>
-    <t>居五英</t>
-  </si>
-  <si>
-    <t>恭二他</t>
-  </si>
-  <si>
-    <t>皆一求</t>
-  </si>
-  <si>
-    <t>公七門</t>
-  </si>
-  <si>
-    <t>伽二邊</t>
-  </si>
-  <si>
-    <t>丩二曾</t>
-  </si>
-  <si>
-    <t>金五柳</t>
-  </si>
-  <si>
-    <t>居二喜</t>
-  </si>
-  <si>
-    <t>牛五英</t>
-  </si>
-  <si>
-    <t>迦一曾</t>
-  </si>
-  <si>
-    <t>恭五時</t>
-  </si>
-  <si>
-    <t>丩五求</t>
-  </si>
-  <si>
-    <t>沽二求</t>
-  </si>
-  <si>
-    <t>居七入</t>
-  </si>
-  <si>
-    <t>規五英</t>
-  </si>
-  <si>
-    <t>皆一曾</t>
-  </si>
-  <si>
-    <t>居二求</t>
-  </si>
-  <si>
-    <t>嬌七門</t>
-  </si>
-  <si>
-    <t>公五地</t>
-  </si>
-  <si>
-    <t>高一求</t>
-  </si>
-  <si>
-    <t>巾五門</t>
-  </si>
-  <si>
-    <t>君一求</t>
-  </si>
-  <si>
-    <t>居七時</t>
-  </si>
-  <si>
-    <t>巾三曾</t>
-  </si>
-  <si>
-    <t>經八英</t>
-  </si>
-  <si>
-    <t>檜三他</t>
-  </si>
-  <si>
-    <t>居五時</t>
-  </si>
-  <si>
-    <t>迦五英</t>
-  </si>
-  <si>
-    <t>巾四邊</t>
-  </si>
-  <si>
-    <t>堅一時</t>
-  </si>
-  <si>
-    <t>居五門</t>
-  </si>
-  <si>
-    <t>沽五雅</t>
-  </si>
-  <si>
-    <t>規一求</t>
   </si>
   <si>
     <t>ham5</t>
@@ -2325,6 +1698,1623 @@
   </si>
   <si>
     <t>tong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khing3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經三去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lik8</t>
+  </si>
+  <si>
+    <t>經八柳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>su3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艍三時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>堅五柳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cun1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>君一出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ting5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經五地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艍二曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經一求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經四地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丩二時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pa1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>膠一邊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ling5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經五柳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kun7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>君七求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uat8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>觀八英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bing5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經五門</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zing3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經三曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公一他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jin5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巾五入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ho5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高五喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經四邊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hue3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>檜三喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khu7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艍七去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hing1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經一喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nai2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>皆二耐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiong7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭七地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siu1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丩一時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gak8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江八語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iang5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姜五英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lau5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交五柳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zing1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經一曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ki5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居五求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kiu7</t>
+  </si>
+  <si>
+    <t>丩七求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ze3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伽三曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經四去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公五地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>堅五喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kim1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金一求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>si1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居一時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hu3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艍三喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艍一英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siong7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭七時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭八時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艍二英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公四曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bun5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>君五門</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居二英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ki3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居三求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zi1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居一曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kuan1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>觀一求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hu1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艍一喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sing3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經三時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zong7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公七曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zai7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>皆七曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tong7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公七地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiann5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驚五地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>it4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巾四英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oo5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沽五英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>uan2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>觀二英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>san1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>干一時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thun1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>君一他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭五地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kang1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江一求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ho7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高七喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hing5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經五喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艍五門</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gai5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>皆五語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiau1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嬌一地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sik8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經八時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iam1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼一英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khi3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居三去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ban7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>干七門</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cian1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>堅一出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艍二出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經四曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tai7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>皆七地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ia7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迦七英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>堅五曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sut8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>君八時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pi7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居七邊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>堅五入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公四邊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kiap4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼四求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lam5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甘五柳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kik8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經八求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siau1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嬌一時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siang1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姜一時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kheeh4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉四去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>so1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高一時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高一地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hue7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>檜七喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lam2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甘二柳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>but8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>君八門</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zing5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經五曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居七英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hoo5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沽五喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jiok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭八入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>規一喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liam5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼五柳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gueh8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>檜八語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>put4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>君四邊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khui1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>規一去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公一喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>noo7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沽七耐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tak8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江八地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公七柳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pai5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>皆五邊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公一去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jit8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巾八入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sing1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經一時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>un2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>君二英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iau7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嬌七英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziam5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼五曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>li2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居二柳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hang5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江五喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khing1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經一去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cip4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金四出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cui1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>規一出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公八邊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boo7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沽七門</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hoo2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沽二喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siau3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嬌三時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uan5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>觀五英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>the5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伽五他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ting1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經一地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>su1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艍一時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丩二英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艍二去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公四求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>huai5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乖五喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hiang1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姜一喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iu1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丩一英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>規三英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ki1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居一求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buan2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>觀二門</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公八門</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kam2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甘二求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ji5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居五入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pi1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居一邊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zia2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迦二曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zi3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居三曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>king2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經二求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pho1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高一頗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lan5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>干五柳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ha7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>膠七喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thian1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>堅一他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公一求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經四頗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khing2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經二去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sa1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>膠一時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>io1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>茄一英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siang5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姜五時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zip8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金八曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kim2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金二求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丩五英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ing2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經二英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gan7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>干七語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zi2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居二曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cenn1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更一出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hik8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經八喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ian1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>堅一英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艍五頗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iak8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姜八英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zing7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經七曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiam5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼五地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艍五語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kua1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓜一求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hoo7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沽七喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tah4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>膠四地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ngau7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交七雅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sim1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金一時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khong3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公三去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sin5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巾五時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居五英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thiong2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭二他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kai1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>皆一求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bong7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公七門</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pe2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伽二邊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丩二曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lim5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金五柳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hi2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居二喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iunn5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛五英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zia1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迦一曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭五時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kiu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丩五求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>koo2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沽二求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ji7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居七入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>規五英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zai1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>皆一曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ki2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居二求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biau7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嬌七門</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ko1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高一求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bin5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巾五門</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kun1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>君一求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>si7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居七時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zin3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巾三曾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ik8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>經八英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thue3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>檜三他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>si5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居五時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ia5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迦五英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pit4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巾四邊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sian1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>堅一時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bi5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>居五門</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ngoo5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沽五雅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kui1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>規一求</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2332,7 +3322,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="42">
+  <fonts count="43">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2624,8 +3614,16 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <color rgb="FFFF0000"/>
+      <name val="吳守禮細明台語注音"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2647,6 +3645,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2728,7 +3732,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2910,6 +3914,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4124,7 +5131,7 @@
       <c r="C3" s="21"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22" t="s">
-        <v>731</v>
+        <v>522</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
@@ -4133,7 +5140,7 @@
       <c r="J3" s="22"/>
       <c r="K3" s="22"/>
       <c r="L3" s="22" t="s">
-        <v>732</v>
+        <v>523</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
@@ -4149,44 +5156,44 @@
     <row r="4" spans="1:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B4" s="25"/>
       <c r="D4" s="26" t="s">
-        <v>318</v>
+        <v>526</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>319</v>
+        <v>522</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>66</v>
+        <v>530</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>320</v>
+        <v>58</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>321</v>
+        <v>533</v>
       </c>
       <c r="I4" s="26"/>
       <c r="J4" s="26" t="s">
-        <v>322</v>
+        <v>535</v>
       </c>
       <c r="K4" s="26" t="s">
-        <v>323</v>
+        <v>537</v>
       </c>
       <c r="L4" s="26" t="s">
-        <v>324</v>
+        <v>523</v>
       </c>
       <c r="M4" s="26" t="s">
-        <v>325</v>
+        <v>540</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>326</v>
+        <v>542</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>327</v>
+        <v>544</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>63</v>
+        <v>546</v>
       </c>
       <c r="Q4" s="26" t="s">
-        <v>328</v>
+        <v>548</v>
       </c>
       <c r="R4" s="26"/>
       <c r="S4" s="27"/>
@@ -4199,7 +5206,7 @@
       <c r="D5" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="54" t="s">
+      <c r="E5" s="61" t="s">
         <v>86</v>
       </c>
       <c r="F5" s="54" t="s">
@@ -4220,7 +5227,7 @@
       <c r="K5" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="54" t="s">
+      <c r="L5" s="61" t="s">
         <v>91</v>
       </c>
       <c r="M5" s="54" t="s">
@@ -4248,44 +5255,44 @@
       <c r="B6" s="30"/>
       <c r="C6" s="31"/>
       <c r="D6" s="32" t="s">
-        <v>503</v>
+        <v>527</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>504</v>
+        <v>529</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>507</v>
+        <v>534</v>
       </c>
       <c r="I6" s="32"/>
       <c r="J6" s="32" t="s">
-        <v>508</v>
+        <v>536</v>
       </c>
       <c r="K6" s="32" t="s">
-        <v>509</v>
+        <v>538</v>
       </c>
       <c r="L6" s="32" t="s">
-        <v>510</v>
+        <v>539</v>
       </c>
       <c r="M6" s="32" t="s">
-        <v>511</v>
+        <v>541</v>
       </c>
       <c r="N6" s="32" t="s">
-        <v>512</v>
+        <v>543</v>
       </c>
       <c r="O6" s="32" t="s">
-        <v>513</v>
+        <v>545</v>
       </c>
       <c r="P6" s="32" t="s">
-        <v>514</v>
+        <v>547</v>
       </c>
       <c r="Q6" s="32" t="s">
-        <v>515</v>
+        <v>549</v>
       </c>
       <c r="R6" s="32"/>
       <c r="S6" s="33"/>
@@ -4315,43 +5322,43 @@
     <row r="8" spans="1:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="25"/>
       <c r="D8" s="26" t="s">
-        <v>329</v>
+        <v>550</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>330</v>
+        <v>552</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>320</v>
+        <v>58</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="26" t="s">
-        <v>331</v>
+        <v>554</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>332</v>
+        <v>556</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>78</v>
+        <v>558</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>50</v>
+        <v>560</v>
       </c>
       <c r="L8" s="26"/>
       <c r="M8" s="26" t="s">
-        <v>333</v>
+        <v>562</v>
       </c>
       <c r="N8" s="26" t="s">
-        <v>75</v>
+        <v>564</v>
       </c>
       <c r="O8" s="26" t="s">
-        <v>334</v>
+        <v>566</v>
       </c>
       <c r="P8" s="26" t="s">
-        <v>335</v>
+        <v>568</v>
       </c>
       <c r="Q8" s="26"/>
       <c r="R8" s="26" t="s">
-        <v>336</v>
+        <v>570</v>
       </c>
       <c r="S8" s="27"/>
       <c r="V8" s="59"/>
@@ -4413,43 +5420,43 @@
     <row r="10" spans="1:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="30"/>
       <c r="D10" s="32" t="s">
-        <v>516</v>
+        <v>551</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>517</v>
+        <v>553</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="G10" s="32"/>
       <c r="H10" s="32" t="s">
-        <v>518</v>
+        <v>555</v>
       </c>
       <c r="I10" s="32" t="s">
-        <v>519</v>
+        <v>557</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>520</v>
+        <v>559</v>
       </c>
       <c r="K10" s="32" t="s">
-        <v>521</v>
+        <v>561</v>
       </c>
       <c r="L10" s="32"/>
       <c r="M10" s="32" t="s">
-        <v>522</v>
+        <v>563</v>
       </c>
       <c r="N10" s="32" t="s">
-        <v>523</v>
+        <v>565</v>
       </c>
       <c r="O10" s="32" t="s">
-        <v>524</v>
+        <v>567</v>
       </c>
       <c r="P10" s="32" t="s">
-        <v>525</v>
+        <v>569</v>
       </c>
       <c r="Q10" s="32"/>
       <c r="R10" s="32" t="s">
-        <v>526</v>
+        <v>571</v>
       </c>
       <c r="S10" s="39"/>
       <c r="V10" s="59"/>
@@ -4466,13 +5473,13 @@
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
       <c r="L11" s="22" t="s">
-        <v>733</v>
+        <v>524</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
       <c r="O11" s="22"/>
       <c r="P11" s="22" t="s">
-        <v>734</v>
+        <v>525</v>
       </c>
       <c r="Q11" s="22"/>
       <c r="R11" s="22"/>
@@ -4481,45 +5488,45 @@
     <row r="12" spans="1:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="25"/>
       <c r="D12" s="26" t="s">
-        <v>337</v>
+        <v>572</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>338</v>
+        <v>574</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>339</v>
+        <v>576</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>340</v>
+        <v>578</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>341</v>
+        <v>580</v>
       </c>
       <c r="I12" s="26"/>
       <c r="J12" s="26" t="s">
-        <v>342</v>
+        <v>582</v>
       </c>
       <c r="K12" s="26" t="s">
-        <v>60</v>
+        <v>584</v>
       </c>
       <c r="L12" s="26" t="s">
-        <v>343</v>
+        <v>524</v>
       </c>
       <c r="M12" s="26" t="s">
-        <v>344</v>
+        <v>588</v>
       </c>
       <c r="N12" s="26"/>
       <c r="O12" s="26" t="s">
-        <v>345</v>
+        <v>590</v>
       </c>
       <c r="P12" s="26" t="s">
-        <v>346</v>
+        <v>525</v>
       </c>
       <c r="Q12" s="26" t="s">
-        <v>347</v>
+        <v>593</v>
       </c>
       <c r="R12" s="26" t="s">
-        <v>348</v>
+        <v>595</v>
       </c>
       <c r="S12" s="27"/>
       <c r="V12" s="59"/>
@@ -4553,7 +5560,7 @@
       <c r="K13" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="L13" s="54" t="s">
+      <c r="L13" s="61" t="s">
         <v>112</v>
       </c>
       <c r="M13" s="54" t="s">
@@ -4565,7 +5572,7 @@
       <c r="O13" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="P13" s="54" t="s">
+      <c r="P13" s="61" t="s">
         <v>115</v>
       </c>
       <c r="Q13" s="54" t="s">
@@ -4580,45 +5587,45 @@
     <row r="14" spans="1:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="30"/>
       <c r="D14" s="32" t="s">
-        <v>527</v>
+        <v>573</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>528</v>
+        <v>575</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>529</v>
+        <v>577</v>
       </c>
       <c r="G14" s="32" t="s">
-        <v>530</v>
+        <v>579</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>531</v>
+        <v>581</v>
       </c>
       <c r="I14" s="32"/>
       <c r="J14" s="32" t="s">
-        <v>532</v>
+        <v>583</v>
       </c>
       <c r="K14" s="32" t="s">
-        <v>533</v>
+        <v>585</v>
       </c>
       <c r="L14" s="32" t="s">
-        <v>534</v>
+        <v>587</v>
       </c>
       <c r="M14" s="32" t="s">
-        <v>535</v>
+        <v>589</v>
       </c>
       <c r="N14" s="32"/>
       <c r="O14" s="32" t="s">
-        <v>536</v>
+        <v>591</v>
       </c>
       <c r="P14" s="32" t="s">
-        <v>537</v>
+        <v>592</v>
       </c>
       <c r="Q14" s="32" t="s">
-        <v>538</v>
+        <v>594</v>
       </c>
       <c r="R14" s="32" t="s">
-        <v>539</v>
+        <v>596</v>
       </c>
       <c r="S14" s="39"/>
       <c r="V14" s="59"/>
@@ -4646,44 +5653,44 @@
     <row r="16" spans="1:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="25"/>
       <c r="D16" s="26" t="s">
-        <v>78</v>
+        <v>558</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>349</v>
+        <v>597</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>350</v>
+        <v>599</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>351</v>
+        <v>601</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>60</v>
+        <v>584</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>79</v>
+        <v>603</v>
       </c>
       <c r="J16" s="26"/>
       <c r="K16" s="26" t="s">
-        <v>73</v>
+        <v>605</v>
       </c>
       <c r="L16" s="26" t="s">
-        <v>352</v>
+        <v>607</v>
       </c>
       <c r="M16" s="26" t="s">
-        <v>353</v>
+        <v>609</v>
       </c>
       <c r="N16" s="26" t="s">
-        <v>49</v>
+        <v>611</v>
       </c>
       <c r="O16" s="26" t="s">
-        <v>354</v>
+        <v>613</v>
       </c>
       <c r="P16" s="26" t="s">
-        <v>355</v>
+        <v>615</v>
       </c>
       <c r="Q16" s="26" t="s">
-        <v>356</v>
+        <v>617</v>
       </c>
       <c r="R16" s="26"/>
       <c r="S16" s="27"/>
@@ -4745,44 +5752,44 @@
     <row r="18" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="30"/>
       <c r="D18" s="32" t="s">
-        <v>520</v>
+        <v>559</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>540</v>
+        <v>598</v>
       </c>
       <c r="F18" s="32" t="s">
-        <v>541</v>
+        <v>600</v>
       </c>
       <c r="G18" s="32" t="s">
-        <v>542</v>
+        <v>602</v>
       </c>
       <c r="H18" s="32" t="s">
-        <v>533</v>
+        <v>585</v>
       </c>
       <c r="I18" s="32" t="s">
-        <v>543</v>
+        <v>604</v>
       </c>
       <c r="J18" s="32"/>
       <c r="K18" s="32" t="s">
-        <v>544</v>
+        <v>606</v>
       </c>
       <c r="L18" s="32" t="s">
-        <v>545</v>
+        <v>608</v>
       </c>
       <c r="M18" s="32" t="s">
-        <v>546</v>
+        <v>610</v>
       </c>
       <c r="N18" s="32" t="s">
-        <v>547</v>
+        <v>612</v>
       </c>
       <c r="O18" s="32" t="s">
-        <v>548</v>
+        <v>614</v>
       </c>
       <c r="P18" s="32" t="s">
-        <v>549</v>
+        <v>616</v>
       </c>
       <c r="Q18" s="32" t="s">
-        <v>550</v>
+        <v>618</v>
       </c>
       <c r="R18" s="32"/>
       <c r="S18" s="39"/>
@@ -4834,7 +5841,7 @@
         <v>5</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>729</v>
+        <v>520</v>
       </c>
       <c r="E21" s="51"/>
       <c r="F21" s="51"/>
@@ -4919,7 +5926,7 @@
         <v>6</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>729</v>
+        <v>520</v>
       </c>
       <c r="E25" s="51"/>
       <c r="F25" s="51"/>
@@ -4989,45 +5996,45 @@
     <row r="28" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="25"/>
       <c r="D28" s="26" t="s">
-        <v>352</v>
+        <v>607</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>357</v>
+        <v>619</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>358</v>
+        <v>621</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>327</v>
+        <v>544</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>63</v>
+        <v>546</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>74</v>
+        <v>623</v>
       </c>
       <c r="J28" s="26" t="s">
-        <v>359</v>
+        <v>625</v>
       </c>
       <c r="K28" s="26"/>
       <c r="L28" s="26" t="s">
-        <v>360</v>
+        <v>627</v>
       </c>
       <c r="M28" s="26" t="s">
-        <v>361</v>
+        <v>629</v>
       </c>
       <c r="N28" s="26" t="s">
-        <v>362</v>
+        <v>631</v>
       </c>
       <c r="O28" s="26" t="s">
-        <v>363</v>
+        <v>633</v>
       </c>
       <c r="P28" s="26" t="s">
-        <v>364</v>
+        <v>635</v>
       </c>
       <c r="Q28" s="26"/>
       <c r="R28" s="26" t="s">
-        <v>716</v>
+        <v>507</v>
       </c>
       <c r="S28" s="27"/>
       <c r="U28" s="43" t="str">
@@ -5096,45 +6103,45 @@
     <row r="30" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="30"/>
       <c r="D30" s="32" t="s">
+        <v>608</v>
+      </c>
+      <c r="E30" s="32" t="s">
+        <v>620</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>622</v>
+      </c>
+      <c r="G30" s="32" t="s">
         <v>545</v>
       </c>
-      <c r="E30" s="32" t="s">
-        <v>551</v>
-      </c>
-      <c r="F30" s="32" t="s">
-        <v>552</v>
-      </c>
-      <c r="G30" s="32" t="s">
-        <v>513</v>
-      </c>
       <c r="H30" s="32" t="s">
-        <v>514</v>
+        <v>547</v>
       </c>
       <c r="I30" s="32" t="s">
-        <v>553</v>
+        <v>624</v>
       </c>
       <c r="J30" s="32" t="s">
-        <v>554</v>
+        <v>626</v>
       </c>
       <c r="K30" s="32"/>
       <c r="L30" s="32" t="s">
-        <v>555</v>
+        <v>628</v>
       </c>
       <c r="M30" s="32" t="s">
-        <v>556</v>
+        <v>630</v>
       </c>
       <c r="N30" s="32" t="s">
-        <v>557</v>
+        <v>632</v>
       </c>
       <c r="O30" s="32" t="s">
-        <v>558</v>
+        <v>634</v>
       </c>
       <c r="P30" s="32" t="s">
-        <v>559</v>
+        <v>636</v>
       </c>
       <c r="Q30" s="32"/>
       <c r="R30" s="32" t="s">
-        <v>723</v>
+        <v>514</v>
       </c>
       <c r="S30" s="39"/>
       <c r="U30" s="43" t="str">
@@ -5170,43 +6177,43 @@
     <row r="32" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B32" s="25"/>
       <c r="D32" s="26" t="s">
-        <v>365</v>
+        <v>638</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>366</v>
+        <v>640</v>
       </c>
       <c r="F32" s="26"/>
       <c r="G32" s="26" t="s">
-        <v>367</v>
+        <v>642</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>368</v>
+        <v>644</v>
       </c>
       <c r="I32" s="26" t="s">
-        <v>369</v>
+        <v>646</v>
       </c>
       <c r="J32" s="26"/>
       <c r="K32" s="26" t="s">
-        <v>370</v>
+        <v>648</v>
       </c>
       <c r="L32" s="26" t="s">
-        <v>370</v>
+        <v>648</v>
       </c>
       <c r="M32" s="26" t="s">
-        <v>332</v>
+        <v>556</v>
       </c>
       <c r="N32" s="26" t="s">
-        <v>332</v>
+        <v>556</v>
       </c>
       <c r="O32" s="26"/>
       <c r="P32" s="26" t="s">
-        <v>371</v>
+        <v>650</v>
       </c>
       <c r="Q32" s="26" t="s">
-        <v>372</v>
+        <v>652</v>
       </c>
       <c r="R32" s="26" t="s">
-        <v>344</v>
+        <v>588</v>
       </c>
       <c r="S32" s="27"/>
       <c r="U32" s="43" t="str">
@@ -5271,43 +6278,43 @@
     <row r="34" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="30"/>
       <c r="D34" s="32" t="s">
-        <v>560</v>
+        <v>639</v>
       </c>
       <c r="E34" s="32" t="s">
-        <v>561</v>
+        <v>641</v>
       </c>
       <c r="F34" s="32"/>
       <c r="G34" s="32" t="s">
-        <v>562</v>
+        <v>643</v>
       </c>
       <c r="H34" s="32" t="s">
-        <v>563</v>
+        <v>645</v>
       </c>
       <c r="I34" s="32" t="s">
-        <v>564</v>
+        <v>647</v>
       </c>
       <c r="J34" s="32"/>
       <c r="K34" s="32" t="s">
-        <v>565</v>
+        <v>649</v>
       </c>
       <c r="L34" s="32" t="s">
-        <v>565</v>
+        <v>649</v>
       </c>
       <c r="M34" s="32" t="s">
-        <v>519</v>
+        <v>557</v>
       </c>
       <c r="N34" s="32" t="s">
-        <v>519</v>
+        <v>557</v>
       </c>
       <c r="O34" s="32"/>
       <c r="P34" s="32" t="s">
-        <v>566</v>
+        <v>651</v>
       </c>
       <c r="Q34" s="32" t="s">
-        <v>567</v>
+        <v>653</v>
       </c>
       <c r="R34" s="32" t="s">
-        <v>535</v>
+        <v>589</v>
       </c>
       <c r="S34" s="39"/>
       <c r="V34" s="15"/>
@@ -5335,43 +6342,43 @@
     <row r="36" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="25"/>
       <c r="D36" s="26" t="s">
-        <v>373</v>
+        <v>654</v>
       </c>
       <c r="E36" s="26"/>
       <c r="F36" s="26" t="s">
-        <v>374</v>
+        <v>656</v>
       </c>
       <c r="G36" s="26" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>375</v>
+        <v>658</v>
       </c>
       <c r="I36" s="26" t="s">
-        <v>376</v>
+        <v>660</v>
       </c>
       <c r="J36" s="26"/>
       <c r="K36" s="26" t="s">
-        <v>377</v>
+        <v>662</v>
       </c>
       <c r="L36" s="26" t="s">
-        <v>79</v>
+        <v>603</v>
       </c>
       <c r="M36" s="26" t="s">
-        <v>378</v>
+        <v>664</v>
       </c>
       <c r="N36" s="26" t="s">
-        <v>379</v>
+        <v>666</v>
       </c>
       <c r="O36" s="26"/>
       <c r="P36" s="26" t="s">
-        <v>380</v>
+        <v>668</v>
       </c>
       <c r="Q36" s="26" t="s">
-        <v>381</v>
+        <v>670</v>
       </c>
       <c r="R36" s="26" t="s">
-        <v>339</v>
+        <v>576</v>
       </c>
       <c r="S36" s="27"/>
       <c r="V36" s="15"/>
@@ -5432,43 +6439,43 @@
     <row r="38" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="30"/>
       <c r="D38" s="32" t="s">
-        <v>568</v>
+        <v>655</v>
       </c>
       <c r="E38" s="32"/>
       <c r="F38" s="32" t="s">
-        <v>569</v>
+        <v>657</v>
       </c>
       <c r="G38" s="32" t="s">
-        <v>599</v>
+        <v>499</v>
       </c>
       <c r="H38" s="32" t="s">
-        <v>570</v>
+        <v>659</v>
       </c>
       <c r="I38" s="32" t="s">
-        <v>571</v>
+        <v>661</v>
       </c>
       <c r="J38" s="32"/>
       <c r="K38" s="32" t="s">
-        <v>572</v>
+        <v>663</v>
       </c>
       <c r="L38" s="32" t="s">
-        <v>543</v>
+        <v>604</v>
       </c>
       <c r="M38" s="32" t="s">
-        <v>573</v>
+        <v>665</v>
       </c>
       <c r="N38" s="32" t="s">
-        <v>574</v>
+        <v>667</v>
       </c>
       <c r="O38" s="32"/>
       <c r="P38" s="32" t="s">
-        <v>575</v>
+        <v>669</v>
       </c>
       <c r="Q38" s="32" t="s">
-        <v>576</v>
+        <v>671</v>
       </c>
       <c r="R38" s="32" t="s">
-        <v>529</v>
+        <v>577</v>
       </c>
       <c r="S38" s="39"/>
       <c r="V38" s="15"/>
@@ -5496,45 +6503,45 @@
     <row r="40" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="25"/>
       <c r="D40" s="26" t="s">
-        <v>340</v>
+        <v>578</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>341</v>
+        <v>580</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>356</v>
+        <v>617</v>
       </c>
       <c r="G40" s="26" t="s">
-        <v>76</v>
+        <v>672</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>357</v>
+        <v>619</v>
       </c>
       <c r="I40" s="26" t="s">
-        <v>382</v>
+        <v>674</v>
       </c>
       <c r="J40" s="26"/>
       <c r="K40" s="26" t="s">
-        <v>383</v>
+        <v>676</v>
       </c>
       <c r="L40" s="26" t="s">
-        <v>78</v>
+        <v>558</v>
       </c>
       <c r="M40" s="26" t="s">
-        <v>356</v>
+        <v>617</v>
       </c>
       <c r="N40" s="26" t="s">
-        <v>384</v>
+        <v>678</v>
       </c>
       <c r="O40" s="26" t="s">
-        <v>385</v>
+        <v>680</v>
       </c>
       <c r="P40" s="26" t="s">
-        <v>354</v>
+        <v>613</v>
       </c>
       <c r="Q40" s="26"/>
       <c r="R40" s="26" t="s">
-        <v>386</v>
+        <v>682</v>
       </c>
       <c r="S40" s="27"/>
       <c r="V40" s="15"/>
@@ -5595,45 +6602,45 @@
     <row r="42" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="30"/>
       <c r="D42" s="32" t="s">
-        <v>530</v>
+        <v>579</v>
       </c>
       <c r="E42" s="32" t="s">
-        <v>531</v>
+        <v>581</v>
       </c>
       <c r="F42" s="32" t="s">
-        <v>550</v>
+        <v>618</v>
       </c>
       <c r="G42" s="32" t="s">
-        <v>577</v>
+        <v>673</v>
       </c>
       <c r="H42" s="32" t="s">
-        <v>551</v>
+        <v>620</v>
       </c>
       <c r="I42" s="32" t="s">
-        <v>578</v>
+        <v>675</v>
       </c>
       <c r="J42" s="32"/>
       <c r="K42" s="32" t="s">
-        <v>579</v>
+        <v>677</v>
       </c>
       <c r="L42" s="32" t="s">
-        <v>520</v>
+        <v>559</v>
       </c>
       <c r="M42" s="32" t="s">
-        <v>550</v>
+        <v>618</v>
       </c>
       <c r="N42" s="32" t="s">
-        <v>580</v>
+        <v>679</v>
       </c>
       <c r="O42" s="32" t="s">
-        <v>581</v>
+        <v>681</v>
       </c>
       <c r="P42" s="32" t="s">
-        <v>548</v>
+        <v>614</v>
       </c>
       <c r="Q42" s="32"/>
       <c r="R42" s="32" t="s">
-        <v>582</v>
+        <v>683</v>
       </c>
       <c r="S42" s="39"/>
       <c r="V42" s="15"/>
@@ -5661,45 +6668,45 @@
     <row r="44" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="25"/>
       <c r="D44" s="26" t="s">
-        <v>381</v>
+        <v>670</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>387</v>
+        <v>684</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>332</v>
+        <v>556</v>
       </c>
       <c r="G44" s="26" t="s">
-        <v>372</v>
+        <v>652</v>
       </c>
       <c r="H44" s="26" t="s">
-        <v>388</v>
+        <v>686</v>
       </c>
       <c r="I44" s="26"/>
       <c r="J44" s="26" t="s">
-        <v>389</v>
+        <v>688</v>
       </c>
       <c r="K44" s="26" t="s">
-        <v>69</v>
+        <v>690</v>
       </c>
       <c r="L44" s="26" t="s">
-        <v>390</v>
+        <v>692</v>
       </c>
       <c r="M44" s="26" t="s">
-        <v>391</v>
+        <v>694</v>
       </c>
       <c r="N44" s="26"/>
       <c r="O44" s="26" t="s">
-        <v>379</v>
+        <v>666</v>
       </c>
       <c r="P44" s="26" t="s">
-        <v>392</v>
+        <v>696</v>
       </c>
       <c r="Q44" s="26" t="s">
-        <v>393</v>
+        <v>698</v>
       </c>
       <c r="R44" s="26" t="s">
-        <v>78</v>
+        <v>558</v>
       </c>
       <c r="S44" s="27"/>
       <c r="V44" s="15"/>
@@ -5760,45 +6767,45 @@
     <row r="46" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="30"/>
       <c r="D46" s="32" t="s">
-        <v>576</v>
+        <v>671</v>
       </c>
       <c r="E46" s="32" t="s">
-        <v>583</v>
+        <v>685</v>
       </c>
       <c r="F46" s="32" t="s">
-        <v>519</v>
+        <v>557</v>
       </c>
       <c r="G46" s="32" t="s">
-        <v>567</v>
+        <v>653</v>
       </c>
       <c r="H46" s="32" t="s">
-        <v>584</v>
+        <v>687</v>
       </c>
       <c r="I46" s="32"/>
       <c r="J46" s="32" t="s">
-        <v>585</v>
+        <v>689</v>
       </c>
       <c r="K46" s="32" t="s">
-        <v>586</v>
+        <v>691</v>
       </c>
       <c r="L46" s="32" t="s">
-        <v>587</v>
+        <v>693</v>
       </c>
       <c r="M46" s="32" t="s">
-        <v>588</v>
+        <v>695</v>
       </c>
       <c r="N46" s="32"/>
       <c r="O46" s="32" t="s">
-        <v>574</v>
+        <v>667</v>
       </c>
       <c r="P46" s="32" t="s">
-        <v>589</v>
+        <v>697</v>
       </c>
       <c r="Q46" s="32" t="s">
-        <v>590</v>
+        <v>699</v>
       </c>
       <c r="R46" s="32" t="s">
-        <v>520</v>
+        <v>559</v>
       </c>
       <c r="S46" s="39"/>
       <c r="V46" s="15"/>
@@ -5827,42 +6834,42 @@
       <c r="B48" s="25"/>
       <c r="D48" s="26"/>
       <c r="E48" s="26" t="s">
-        <v>394</v>
+        <v>700</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>395</v>
+        <v>702</v>
       </c>
       <c r="G48" s="26" t="s">
-        <v>351</v>
+        <v>601</v>
       </c>
       <c r="H48" s="26" t="s">
-        <v>380</v>
+        <v>668</v>
       </c>
       <c r="I48" s="26"/>
       <c r="J48" s="26" t="s">
-        <v>396</v>
+        <v>704</v>
       </c>
       <c r="K48" s="26" t="s">
-        <v>397</v>
+        <v>706</v>
       </c>
       <c r="L48" s="26" t="s">
-        <v>356</v>
+        <v>617</v>
       </c>
       <c r="M48" s="26" t="s">
-        <v>398</v>
+        <v>708</v>
       </c>
       <c r="N48" s="26"/>
       <c r="O48" s="26" t="s">
-        <v>325</v>
+        <v>540</v>
       </c>
       <c r="P48" s="26" t="s">
-        <v>372</v>
+        <v>652</v>
       </c>
       <c r="Q48" s="26" t="s">
-        <v>399</v>
+        <v>710</v>
       </c>
       <c r="R48" s="26" t="s">
-        <v>400</v>
+        <v>712</v>
       </c>
       <c r="S48" s="27"/>
       <c r="V48" s="15"/>
@@ -5924,42 +6931,42 @@
       <c r="B50" s="30"/>
       <c r="D50" s="32"/>
       <c r="E50" s="32" t="s">
-        <v>591</v>
+        <v>701</v>
       </c>
       <c r="F50" s="32" t="s">
-        <v>592</v>
+        <v>703</v>
       </c>
       <c r="G50" s="32" t="s">
-        <v>542</v>
+        <v>602</v>
       </c>
       <c r="H50" s="32" t="s">
-        <v>575</v>
+        <v>669</v>
       </c>
       <c r="I50" s="32"/>
       <c r="J50" s="32" t="s">
-        <v>593</v>
+        <v>705</v>
       </c>
       <c r="K50" s="32" t="s">
-        <v>594</v>
+        <v>707</v>
       </c>
       <c r="L50" s="32" t="s">
-        <v>550</v>
+        <v>618</v>
       </c>
       <c r="M50" s="32" t="s">
-        <v>595</v>
+        <v>709</v>
       </c>
       <c r="N50" s="32"/>
       <c r="O50" s="32" t="s">
-        <v>511</v>
+        <v>541</v>
       </c>
       <c r="P50" s="32" t="s">
-        <v>567</v>
+        <v>653</v>
       </c>
       <c r="Q50" s="32" t="s">
-        <v>596</v>
+        <v>711</v>
       </c>
       <c r="R50" s="32" t="s">
-        <v>597</v>
+        <v>713</v>
       </c>
       <c r="S50" s="39"/>
       <c r="V50" s="15"/>
@@ -6013,7 +7020,7 @@
         <v>179</v>
       </c>
       <c r="E53" s="51" t="s">
-        <v>729</v>
+        <v>520</v>
       </c>
       <c r="F53" s="51"/>
       <c r="G53" s="51"/>
@@ -6097,7 +7104,7 @@
         <v>14</v>
       </c>
       <c r="D57" s="51" t="s">
-        <v>729</v>
+        <v>520</v>
       </c>
       <c r="E57" s="51"/>
       <c r="F57" s="51"/>
@@ -6159,45 +7166,45 @@
     <row r="60" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B60" s="25"/>
       <c r="D60" s="26" t="s">
-        <v>401</v>
+        <v>714</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>358</v>
+        <v>621</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>717</v>
+        <v>508</v>
       </c>
       <c r="G60" s="26" t="s">
-        <v>352</v>
+        <v>607</v>
       </c>
       <c r="H60" s="26" t="s">
-        <v>402</v>
+        <v>498</v>
       </c>
       <c r="I60" s="26" t="s">
-        <v>402</v>
+        <v>498</v>
       </c>
       <c r="J60" s="26"/>
       <c r="K60" s="26" t="s">
-        <v>403</v>
+        <v>717</v>
       </c>
       <c r="L60" s="26" t="s">
-        <v>404</v>
+        <v>719</v>
       </c>
       <c r="M60" s="26" t="s">
-        <v>405</v>
+        <v>721</v>
       </c>
       <c r="N60" s="26" t="s">
-        <v>406</v>
+        <v>723</v>
       </c>
       <c r="O60" s="26"/>
       <c r="P60" s="26" t="s">
-        <v>376</v>
+        <v>660</v>
       </c>
       <c r="Q60" s="26" t="s">
-        <v>407</v>
+        <v>725</v>
       </c>
       <c r="R60" s="26" t="s">
-        <v>408</v>
+        <v>727</v>
       </c>
       <c r="S60" s="27"/>
       <c r="V60" s="15"/>
@@ -6258,45 +7265,45 @@
     <row r="62" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="30"/>
       <c r="D62" s="32" t="s">
-        <v>598</v>
+        <v>715</v>
       </c>
       <c r="E62" s="32" t="s">
-        <v>552</v>
+        <v>622</v>
       </c>
       <c r="F62" s="32" t="s">
-        <v>724</v>
+        <v>515</v>
       </c>
       <c r="G62" s="32" t="s">
-        <v>545</v>
+        <v>608</v>
       </c>
       <c r="H62" s="32" t="s">
-        <v>599</v>
+        <v>716</v>
       </c>
       <c r="I62" s="32" t="s">
-        <v>599</v>
+        <v>716</v>
       </c>
       <c r="J62" s="32"/>
       <c r="K62" s="32" t="s">
-        <v>600</v>
+        <v>718</v>
       </c>
       <c r="L62" s="32" t="s">
-        <v>601</v>
+        <v>720</v>
       </c>
       <c r="M62" s="32" t="s">
-        <v>602</v>
+        <v>722</v>
       </c>
       <c r="N62" s="32" t="s">
-        <v>603</v>
+        <v>724</v>
       </c>
       <c r="O62" s="32"/>
       <c r="P62" s="32" t="s">
-        <v>571</v>
+        <v>661</v>
       </c>
       <c r="Q62" s="32" t="s">
-        <v>604</v>
+        <v>726</v>
       </c>
       <c r="R62" s="32" t="s">
-        <v>605</v>
+        <v>728</v>
       </c>
       <c r="S62" s="39"/>
       <c r="V62" s="15"/>
@@ -6324,43 +7331,43 @@
     <row r="64" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B64" s="25"/>
       <c r="D64" s="26" t="s">
-        <v>370</v>
+        <v>648</v>
       </c>
       <c r="E64" s="26"/>
       <c r="F64" s="26" t="s">
-        <v>409</v>
+        <v>729</v>
       </c>
       <c r="G64" s="26" t="s">
-        <v>410</v>
+        <v>731</v>
       </c>
       <c r="H64" s="26" t="s">
-        <v>411</v>
+        <v>733</v>
       </c>
       <c r="I64" s="26" t="s">
-        <v>412</v>
+        <v>735</v>
       </c>
       <c r="J64" s="26"/>
       <c r="K64" s="26" t="s">
-        <v>413</v>
+        <v>737</v>
       </c>
       <c r="L64" s="26" t="s">
-        <v>77</v>
+        <v>739</v>
       </c>
       <c r="M64" s="26" t="s">
-        <v>414</v>
+        <v>741</v>
       </c>
       <c r="N64" s="26" t="s">
-        <v>415</v>
+        <v>743</v>
       </c>
       <c r="O64" s="26"/>
       <c r="P64" s="26" t="s">
-        <v>366</v>
+        <v>640</v>
       </c>
       <c r="Q64" s="26" t="s">
-        <v>339</v>
+        <v>576</v>
       </c>
       <c r="R64" s="26" t="s">
-        <v>416</v>
+        <v>745</v>
       </c>
       <c r="S64" s="27"/>
       <c r="V64" s="15"/>
@@ -6421,43 +7428,43 @@
     <row r="66" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B66" s="30"/>
       <c r="D66" s="32" t="s">
-        <v>565</v>
+        <v>649</v>
       </c>
       <c r="E66" s="32"/>
       <c r="F66" s="32" t="s">
-        <v>606</v>
+        <v>730</v>
       </c>
       <c r="G66" s="32" t="s">
-        <v>607</v>
+        <v>732</v>
       </c>
       <c r="H66" s="32" t="s">
-        <v>608</v>
+        <v>734</v>
       </c>
       <c r="I66" s="32" t="s">
-        <v>609</v>
+        <v>736</v>
       </c>
       <c r="J66" s="32"/>
       <c r="K66" s="32" t="s">
-        <v>610</v>
+        <v>738</v>
       </c>
       <c r="L66" s="32" t="s">
-        <v>611</v>
+        <v>740</v>
       </c>
       <c r="M66" s="32" t="s">
-        <v>612</v>
+        <v>742</v>
       </c>
       <c r="N66" s="32" t="s">
-        <v>613</v>
+        <v>744</v>
       </c>
       <c r="O66" s="32"/>
       <c r="P66" s="32" t="s">
-        <v>561</v>
+        <v>641</v>
       </c>
       <c r="Q66" s="32" t="s">
-        <v>529</v>
+        <v>577</v>
       </c>
       <c r="R66" s="32" t="s">
-        <v>614</v>
+        <v>746</v>
       </c>
       <c r="S66" s="39"/>
       <c r="V66" s="15"/>
@@ -6485,43 +7492,43 @@
     <row r="68" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B68" s="25"/>
       <c r="D68" s="26" t="s">
-        <v>371</v>
+        <v>650</v>
       </c>
       <c r="E68" s="26"/>
       <c r="F68" s="26" t="s">
-        <v>391</v>
+        <v>694</v>
       </c>
       <c r="G68" s="26" t="s">
-        <v>417</v>
+        <v>747</v>
       </c>
       <c r="H68" s="26" t="s">
-        <v>405</v>
+        <v>721</v>
       </c>
       <c r="I68" s="26" t="s">
-        <v>418</v>
+        <v>749</v>
       </c>
       <c r="J68" s="26"/>
       <c r="K68" s="26" t="s">
-        <v>718</v>
+        <v>509</v>
       </c>
       <c r="L68" s="26" t="s">
-        <v>419</v>
+        <v>751</v>
       </c>
       <c r="M68" s="26" t="s">
-        <v>420</v>
+        <v>753</v>
       </c>
       <c r="N68" s="26" t="s">
-        <v>421</v>
+        <v>755</v>
       </c>
       <c r="O68" s="26"/>
       <c r="P68" s="26" t="s">
-        <v>422</v>
+        <v>757</v>
       </c>
       <c r="Q68" s="26" t="s">
-        <v>423</v>
+        <v>759</v>
       </c>
       <c r="R68" s="26" t="s">
-        <v>330</v>
+        <v>552</v>
       </c>
       <c r="S68" s="27"/>
       <c r="V68" s="15"/>
@@ -6582,43 +7589,43 @@
     <row r="70" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="30"/>
       <c r="D70" s="32" t="s">
-        <v>566</v>
+        <v>651</v>
       </c>
       <c r="E70" s="32"/>
       <c r="F70" s="32" t="s">
-        <v>588</v>
+        <v>695</v>
       </c>
       <c r="G70" s="32" t="s">
-        <v>615</v>
+        <v>748</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>602</v>
+        <v>722</v>
       </c>
       <c r="I70" s="32" t="s">
-        <v>616</v>
+        <v>750</v>
       </c>
       <c r="J70" s="32"/>
       <c r="K70" s="32" t="s">
-        <v>725</v>
+        <v>516</v>
       </c>
       <c r="L70" s="32" t="s">
-        <v>617</v>
+        <v>752</v>
       </c>
       <c r="M70" s="32" t="s">
-        <v>618</v>
+        <v>754</v>
       </c>
       <c r="N70" s="32" t="s">
-        <v>619</v>
+        <v>756</v>
       </c>
       <c r="O70" s="32"/>
       <c r="P70" s="32" t="s">
-        <v>620</v>
+        <v>758</v>
       </c>
       <c r="Q70" s="32" t="s">
-        <v>621</v>
+        <v>760</v>
       </c>
       <c r="R70" s="32" t="s">
-        <v>517</v>
+        <v>553</v>
       </c>
       <c r="S70" s="39"/>
       <c r="V70" s="15"/>
@@ -6646,43 +7653,43 @@
     <row r="72" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B72" s="25"/>
       <c r="D72" s="26" t="s">
-        <v>330</v>
+        <v>552</v>
       </c>
       <c r="E72" s="26"/>
       <c r="F72" s="26" t="s">
-        <v>424</v>
+        <v>761</v>
       </c>
       <c r="G72" s="26" t="s">
-        <v>425</v>
+        <v>763</v>
       </c>
       <c r="H72" s="26" t="s">
-        <v>426</v>
+        <v>765</v>
       </c>
       <c r="I72" s="26" t="s">
-        <v>427</v>
+        <v>767</v>
       </c>
       <c r="J72" s="26"/>
       <c r="K72" s="26" t="s">
-        <v>428</v>
+        <v>769</v>
       </c>
       <c r="L72" s="26" t="s">
-        <v>71</v>
+        <v>771</v>
       </c>
       <c r="M72" s="26" t="s">
-        <v>341</v>
+        <v>580</v>
       </c>
       <c r="N72" s="26" t="s">
-        <v>382</v>
+        <v>674</v>
       </c>
       <c r="O72" s="26"/>
       <c r="P72" s="26" t="s">
-        <v>381</v>
+        <v>670</v>
       </c>
       <c r="Q72" s="26" t="s">
-        <v>429</v>
+        <v>773</v>
       </c>
       <c r="R72" s="26" t="s">
-        <v>430</v>
+        <v>775</v>
       </c>
       <c r="S72" s="27"/>
       <c r="V72" s="15"/>
@@ -6743,43 +7750,43 @@
     <row r="74" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="30"/>
       <c r="D74" s="32" t="s">
-        <v>517</v>
+        <v>553</v>
       </c>
       <c r="E74" s="32"/>
       <c r="F74" s="32" t="s">
-        <v>622</v>
+        <v>762</v>
       </c>
       <c r="G74" s="32" t="s">
-        <v>623</v>
+        <v>764</v>
       </c>
       <c r="H74" s="32" t="s">
-        <v>624</v>
+        <v>766</v>
       </c>
       <c r="I74" s="32" t="s">
-        <v>625</v>
+        <v>768</v>
       </c>
       <c r="J74" s="32"/>
       <c r="K74" s="32" t="s">
-        <v>626</v>
+        <v>770</v>
       </c>
       <c r="L74" s="32" t="s">
-        <v>627</v>
+        <v>772</v>
       </c>
       <c r="M74" s="32" t="s">
-        <v>531</v>
+        <v>581</v>
       </c>
       <c r="N74" s="32" t="s">
-        <v>578</v>
+        <v>675</v>
       </c>
       <c r="O74" s="32"/>
       <c r="P74" s="32" t="s">
-        <v>576</v>
+        <v>671</v>
       </c>
       <c r="Q74" s="32" t="s">
-        <v>628</v>
+        <v>774</v>
       </c>
       <c r="R74" s="32" t="s">
-        <v>629</v>
+        <v>776</v>
       </c>
       <c r="S74" s="39"/>
       <c r="V74" s="15"/>
@@ -6807,43 +7814,43 @@
     <row r="76" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="25"/>
       <c r="D76" s="26" t="s">
-        <v>431</v>
+        <v>777</v>
       </c>
       <c r="E76" s="26" t="s">
-        <v>432</v>
+        <v>779</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>433</v>
+        <v>781</v>
       </c>
       <c r="G76" s="26"/>
       <c r="H76" s="26" t="s">
-        <v>434</v>
+        <v>783</v>
       </c>
       <c r="I76" s="26" t="s">
-        <v>719</v>
+        <v>510</v>
       </c>
       <c r="J76" s="26" t="s">
-        <v>435</v>
+        <v>785</v>
       </c>
       <c r="K76" s="26" t="s">
-        <v>436</v>
+        <v>787</v>
       </c>
       <c r="L76" s="26"/>
       <c r="M76" s="26" t="s">
-        <v>437</v>
+        <v>789</v>
       </c>
       <c r="N76" s="26" t="s">
-        <v>438</v>
+        <v>791</v>
       </c>
       <c r="O76" s="26" t="s">
-        <v>390</v>
+        <v>692</v>
       </c>
       <c r="P76" s="26" t="s">
-        <v>386</v>
+        <v>682</v>
       </c>
       <c r="Q76" s="26"/>
       <c r="R76" s="26" t="s">
-        <v>62</v>
+        <v>793</v>
       </c>
       <c r="S76" s="27"/>
       <c r="V76" s="15"/>
@@ -6904,43 +7911,43 @@
     <row r="78" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="30"/>
       <c r="D78" s="32" t="s">
-        <v>630</v>
+        <v>778</v>
       </c>
       <c r="E78" s="32" t="s">
-        <v>631</v>
+        <v>780</v>
       </c>
       <c r="F78" s="32" t="s">
-        <v>632</v>
+        <v>782</v>
       </c>
       <c r="G78" s="32"/>
       <c r="H78" s="32" t="s">
-        <v>633</v>
+        <v>784</v>
       </c>
       <c r="I78" s="32" t="s">
-        <v>726</v>
+        <v>517</v>
       </c>
       <c r="J78" s="32" t="s">
-        <v>634</v>
+        <v>786</v>
       </c>
       <c r="K78" s="32" t="s">
-        <v>635</v>
+        <v>788</v>
       </c>
       <c r="L78" s="32"/>
       <c r="M78" s="32" t="s">
-        <v>636</v>
+        <v>790</v>
       </c>
       <c r="N78" s="32" t="s">
-        <v>637</v>
+        <v>792</v>
       </c>
       <c r="O78" s="32" t="s">
-        <v>587</v>
+        <v>693</v>
       </c>
       <c r="P78" s="32" t="s">
-        <v>582</v>
+        <v>683</v>
       </c>
       <c r="Q78" s="32"/>
       <c r="R78" s="32" t="s">
-        <v>638</v>
+        <v>794</v>
       </c>
       <c r="S78" s="39"/>
       <c r="V78" s="15"/>
@@ -6968,19 +7975,19 @@
     <row r="80" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B80" s="25"/>
       <c r="D80" s="26" t="s">
-        <v>69</v>
+        <v>690</v>
       </c>
       <c r="E80" s="26" t="s">
-        <v>439</v>
+        <v>795</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>61</v>
+        <v>797</v>
       </c>
       <c r="G80" s="26" t="s">
-        <v>440</v>
+        <v>799</v>
       </c>
       <c r="H80" s="26" t="s">
-        <v>354</v>
+        <v>613</v>
       </c>
       <c r="I80" s="26"/>
       <c r="J80" s="26"/>
@@ -7019,7 +8026,7 @@
         <v>38</v>
       </c>
       <c r="J81" s="51" t="s">
-        <v>729</v>
+        <v>520</v>
       </c>
       <c r="K81" s="51"/>
       <c r="L81" s="51"/>
@@ -7035,19 +8042,19 @@
     <row r="82" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B82" s="30"/>
       <c r="D82" s="32" t="s">
-        <v>586</v>
+        <v>691</v>
       </c>
       <c r="E82" s="32" t="s">
-        <v>639</v>
+        <v>796</v>
       </c>
       <c r="F82" s="32" t="s">
-        <v>640</v>
+        <v>798</v>
       </c>
       <c r="G82" s="32" t="s">
-        <v>641</v>
+        <v>800</v>
       </c>
       <c r="H82" s="32" t="s">
-        <v>548</v>
+        <v>614</v>
       </c>
       <c r="I82" s="32"/>
       <c r="J82" s="32"/>
@@ -7108,7 +8115,7 @@
         <v>21</v>
       </c>
       <c r="D85" s="51" t="s">
-        <v>729</v>
+        <v>520</v>
       </c>
       <c r="E85" s="51"/>
       <c r="F85" s="51"/>
@@ -7170,45 +8177,45 @@
     <row r="88" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B88" s="25"/>
       <c r="D88" s="26" t="s">
-        <v>64</v>
+        <v>801</v>
       </c>
       <c r="E88" s="26" t="s">
-        <v>401</v>
+        <v>714</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>321</v>
+        <v>533</v>
       </c>
       <c r="G88" s="26" t="s">
-        <v>50</v>
+        <v>560</v>
       </c>
       <c r="H88" s="26" t="s">
-        <v>441</v>
+        <v>803</v>
       </c>
       <c r="I88" s="26" t="s">
-        <v>330</v>
+        <v>552</v>
       </c>
       <c r="J88" s="26"/>
       <c r="K88" s="26" t="s">
-        <v>442</v>
+        <v>805</v>
       </c>
       <c r="L88" s="26" t="s">
-        <v>443</v>
+        <v>807</v>
       </c>
       <c r="M88" s="26" t="s">
-        <v>405</v>
+        <v>721</v>
       </c>
       <c r="N88" s="26" t="s">
-        <v>444</v>
+        <v>523</v>
       </c>
       <c r="O88" s="26"/>
       <c r="P88" s="26" t="s">
-        <v>79</v>
+        <v>603</v>
       </c>
       <c r="Q88" s="26" t="s">
-        <v>445</v>
+        <v>809</v>
       </c>
       <c r="R88" s="26" t="s">
-        <v>446</v>
+        <v>811</v>
       </c>
       <c r="S88" s="27"/>
       <c r="V88" s="15"/>
@@ -7269,45 +8276,45 @@
     <row r="90" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B90" s="30"/>
       <c r="D90" s="32" t="s">
-        <v>642</v>
+        <v>802</v>
       </c>
       <c r="E90" s="32" t="s">
-        <v>598</v>
+        <v>715</v>
       </c>
       <c r="F90" s="32" t="s">
-        <v>507</v>
+        <v>534</v>
       </c>
       <c r="G90" s="32" t="s">
-        <v>521</v>
+        <v>561</v>
       </c>
       <c r="H90" s="32" t="s">
-        <v>643</v>
+        <v>804</v>
       </c>
       <c r="I90" s="32" t="s">
-        <v>517</v>
+        <v>553</v>
       </c>
       <c r="J90" s="32"/>
       <c r="K90" s="32" t="s">
-        <v>644</v>
+        <v>806</v>
       </c>
       <c r="L90" s="32" t="s">
-        <v>645</v>
+        <v>808</v>
       </c>
       <c r="M90" s="32" t="s">
-        <v>602</v>
+        <v>722</v>
       </c>
       <c r="N90" s="32" t="s">
-        <v>646</v>
+        <v>539</v>
       </c>
       <c r="O90" s="32"/>
       <c r="P90" s="32" t="s">
-        <v>543</v>
+        <v>604</v>
       </c>
       <c r="Q90" s="32" t="s">
-        <v>647</v>
+        <v>810</v>
       </c>
       <c r="R90" s="32" t="s">
-        <v>648</v>
+        <v>812</v>
       </c>
       <c r="S90" s="39"/>
       <c r="V90" s="15"/>
@@ -7335,43 +8342,43 @@
     <row r="92" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B92" s="25"/>
       <c r="D92" s="26" t="s">
-        <v>447</v>
+        <v>813</v>
       </c>
       <c r="E92" s="26"/>
       <c r="F92" s="26" t="s">
-        <v>363</v>
+        <v>633</v>
       </c>
       <c r="G92" s="26" t="s">
-        <v>448</v>
+        <v>815</v>
       </c>
       <c r="H92" s="26" t="s">
-        <v>378</v>
+        <v>664</v>
       </c>
       <c r="I92" s="26" t="s">
-        <v>449</v>
+        <v>817</v>
       </c>
       <c r="J92" s="26"/>
       <c r="K92" s="26" t="s">
-        <v>450</v>
+        <v>819</v>
       </c>
       <c r="L92" s="26" t="s">
-        <v>451</v>
+        <v>821</v>
       </c>
       <c r="M92" s="26" t="s">
-        <v>452</v>
+        <v>823</v>
       </c>
       <c r="N92" s="26" t="s">
-        <v>453</v>
+        <v>825</v>
       </c>
       <c r="O92" s="26"/>
       <c r="P92" s="26" t="s">
-        <v>454</v>
+        <v>827</v>
       </c>
       <c r="Q92" s="26" t="s">
-        <v>443</v>
+        <v>807</v>
       </c>
       <c r="R92" s="26" t="s">
-        <v>455</v>
+        <v>829</v>
       </c>
       <c r="S92" s="27"/>
       <c r="V92" s="15"/>
@@ -7432,43 +8439,43 @@
     <row r="94" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B94" s="30"/>
       <c r="D94" s="32" t="s">
-        <v>649</v>
+        <v>814</v>
       </c>
       <c r="E94" s="32"/>
       <c r="F94" s="32" t="s">
-        <v>558</v>
+        <v>634</v>
       </c>
       <c r="G94" s="32" t="s">
-        <v>650</v>
+        <v>816</v>
       </c>
       <c r="H94" s="32" t="s">
-        <v>573</v>
+        <v>665</v>
       </c>
       <c r="I94" s="32" t="s">
-        <v>651</v>
+        <v>818</v>
       </c>
       <c r="J94" s="32"/>
       <c r="K94" s="32" t="s">
-        <v>652</v>
+        <v>820</v>
       </c>
       <c r="L94" s="32" t="s">
-        <v>653</v>
+        <v>822</v>
       </c>
       <c r="M94" s="32" t="s">
-        <v>654</v>
+        <v>824</v>
       </c>
       <c r="N94" s="32" t="s">
-        <v>655</v>
+        <v>826</v>
       </c>
       <c r="O94" s="32"/>
       <c r="P94" s="32" t="s">
-        <v>656</v>
+        <v>828</v>
       </c>
       <c r="Q94" s="32" t="s">
-        <v>645</v>
+        <v>808</v>
       </c>
       <c r="R94" s="32" t="s">
-        <v>657</v>
+        <v>830</v>
       </c>
       <c r="S94" s="39"/>
       <c r="V94" s="15"/>
@@ -7496,43 +8503,43 @@
     <row r="96" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B96" s="25"/>
       <c r="D96" s="26" t="s">
-        <v>456</v>
+        <v>831</v>
       </c>
       <c r="E96" s="26"/>
       <c r="F96" s="26" t="s">
-        <v>457</v>
+        <v>833</v>
       </c>
       <c r="G96" s="26" t="s">
-        <v>458</v>
+        <v>835</v>
       </c>
       <c r="H96" s="26" t="s">
-        <v>720</v>
+        <v>511</v>
       </c>
       <c r="I96" s="26" t="s">
-        <v>443</v>
+        <v>807</v>
       </c>
       <c r="J96" s="26"/>
       <c r="K96" s="26" t="s">
-        <v>721</v>
+        <v>512</v>
       </c>
       <c r="L96" s="26" t="s">
-        <v>721</v>
+        <v>512</v>
       </c>
       <c r="M96" s="26" t="s">
-        <v>459</v>
+        <v>837</v>
       </c>
       <c r="N96" s="26" t="s">
-        <v>459</v>
+        <v>837</v>
       </c>
       <c r="O96" s="26"/>
       <c r="P96" s="26" t="s">
-        <v>439</v>
+        <v>795</v>
       </c>
       <c r="Q96" s="26" t="s">
-        <v>460</v>
+        <v>839</v>
       </c>
       <c r="R96" s="26" t="s">
-        <v>368</v>
+        <v>644</v>
       </c>
       <c r="S96" s="27"/>
       <c r="V96" s="15"/>
@@ -7593,43 +8600,43 @@
     <row r="98" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B98" s="30"/>
       <c r="D98" s="32" t="s">
-        <v>658</v>
+        <v>832</v>
       </c>
       <c r="E98" s="32"/>
       <c r="F98" s="32" t="s">
-        <v>659</v>
+        <v>834</v>
       </c>
       <c r="G98" s="32" t="s">
-        <v>660</v>
+        <v>836</v>
       </c>
       <c r="H98" s="32" t="s">
-        <v>727</v>
+        <v>518</v>
       </c>
       <c r="I98" s="32" t="s">
-        <v>645</v>
+        <v>808</v>
       </c>
       <c r="J98" s="32"/>
       <c r="K98" s="32" t="s">
-        <v>728</v>
+        <v>519</v>
       </c>
       <c r="L98" s="32" t="s">
-        <v>728</v>
+        <v>519</v>
       </c>
       <c r="M98" s="32" t="s">
-        <v>661</v>
+        <v>838</v>
       </c>
       <c r="N98" s="32" t="s">
-        <v>661</v>
+        <v>838</v>
       </c>
       <c r="O98" s="32"/>
       <c r="P98" s="32" t="s">
-        <v>639</v>
+        <v>796</v>
       </c>
       <c r="Q98" s="32" t="s">
-        <v>662</v>
+        <v>840</v>
       </c>
       <c r="R98" s="32" t="s">
-        <v>563</v>
+        <v>645</v>
       </c>
       <c r="S98" s="39"/>
       <c r="V98" s="15"/>
@@ -7657,43 +8664,43 @@
     <row r="100" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B100" s="25"/>
       <c r="D100" s="26" t="s">
-        <v>461</v>
+        <v>841</v>
       </c>
       <c r="E100" s="26" t="s">
-        <v>363</v>
+        <v>633</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>412</v>
+        <v>735</v>
       </c>
       <c r="G100" s="26"/>
       <c r="H100" s="26" t="s">
-        <v>370</v>
+        <v>648</v>
       </c>
       <c r="I100" s="26" t="s">
-        <v>404</v>
+        <v>719</v>
       </c>
       <c r="J100" s="26" t="s">
-        <v>379</v>
+        <v>666</v>
       </c>
       <c r="K100" s="26" t="s">
-        <v>417</v>
+        <v>747</v>
       </c>
       <c r="L100" s="26"/>
       <c r="M100" s="26" t="s">
-        <v>462</v>
+        <v>843</v>
       </c>
       <c r="N100" s="26" t="s">
-        <v>447</v>
+        <v>813</v>
       </c>
       <c r="O100" s="26" t="s">
-        <v>463</v>
+        <v>845</v>
       </c>
       <c r="P100" s="26" t="s">
-        <v>348</v>
+        <v>595</v>
       </c>
       <c r="Q100" s="26"/>
       <c r="R100" s="26" t="s">
-        <v>464</v>
+        <v>847</v>
       </c>
       <c r="S100" s="27"/>
       <c r="V100" s="15"/>
@@ -7754,43 +8761,43 @@
     <row r="102" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B102" s="30"/>
       <c r="D102" s="32" t="s">
-        <v>663</v>
+        <v>842</v>
       </c>
       <c r="E102" s="32" t="s">
-        <v>558</v>
+        <v>634</v>
       </c>
       <c r="F102" s="32" t="s">
-        <v>609</v>
+        <v>736</v>
       </c>
       <c r="G102" s="32"/>
       <c r="H102" s="32" t="s">
-        <v>565</v>
+        <v>649</v>
       </c>
       <c r="I102" s="32" t="s">
-        <v>601</v>
+        <v>720</v>
       </c>
       <c r="J102" s="32" t="s">
-        <v>574</v>
+        <v>667</v>
       </c>
       <c r="K102" s="32" t="s">
-        <v>615</v>
+        <v>748</v>
       </c>
       <c r="L102" s="32"/>
       <c r="M102" s="32" t="s">
-        <v>664</v>
+        <v>844</v>
       </c>
       <c r="N102" s="32" t="s">
-        <v>649</v>
+        <v>814</v>
       </c>
       <c r="O102" s="32" t="s">
-        <v>665</v>
+        <v>846</v>
       </c>
       <c r="P102" s="32" t="s">
-        <v>539</v>
+        <v>596</v>
       </c>
       <c r="Q102" s="32"/>
       <c r="R102" s="32" t="s">
-        <v>666</v>
+        <v>848</v>
       </c>
       <c r="S102" s="39"/>
       <c r="V102" s="15"/>
@@ -7818,43 +8825,43 @@
     <row r="104" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B104" s="25"/>
       <c r="D104" s="26" t="s">
-        <v>456</v>
+        <v>831</v>
       </c>
       <c r="E104" s="26" t="s">
-        <v>465</v>
+        <v>849</v>
       </c>
       <c r="F104" s="26" t="s">
-        <v>333</v>
+        <v>562</v>
       </c>
       <c r="G104" s="26"/>
       <c r="H104" s="26" t="s">
-        <v>466</v>
+        <v>851</v>
       </c>
       <c r="I104" s="26" t="s">
-        <v>467</v>
+        <v>853</v>
       </c>
       <c r="J104" s="26" t="s">
-        <v>72</v>
+        <v>855</v>
       </c>
       <c r="K104" s="26" t="s">
-        <v>468</v>
+        <v>857</v>
       </c>
       <c r="L104" s="26"/>
       <c r="M104" s="26" t="s">
-        <v>380</v>
+        <v>668</v>
       </c>
       <c r="N104" s="26" t="s">
-        <v>469</v>
+        <v>859</v>
       </c>
       <c r="O104" s="26" t="s">
-        <v>50</v>
+        <v>560</v>
       </c>
       <c r="P104" s="26" t="s">
-        <v>69</v>
+        <v>690</v>
       </c>
       <c r="Q104" s="26"/>
       <c r="R104" s="26" t="s">
-        <v>428</v>
+        <v>769</v>
       </c>
       <c r="S104" s="27"/>
       <c r="V104" s="15"/>
@@ -7915,43 +8922,43 @@
     <row r="106" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B106" s="30"/>
       <c r="D106" s="32" t="s">
-        <v>658</v>
+        <v>832</v>
       </c>
       <c r="E106" s="32" t="s">
-        <v>667</v>
+        <v>850</v>
       </c>
       <c r="F106" s="32" t="s">
-        <v>522</v>
+        <v>563</v>
       </c>
       <c r="G106" s="32"/>
       <c r="H106" s="32" t="s">
-        <v>668</v>
+        <v>852</v>
       </c>
       <c r="I106" s="32" t="s">
-        <v>669</v>
+        <v>854</v>
       </c>
       <c r="J106" s="32" t="s">
-        <v>670</v>
+        <v>856</v>
       </c>
       <c r="K106" s="32" t="s">
-        <v>671</v>
+        <v>858</v>
       </c>
       <c r="L106" s="32"/>
       <c r="M106" s="32" t="s">
-        <v>575</v>
+        <v>669</v>
       </c>
       <c r="N106" s="32" t="s">
-        <v>672</v>
+        <v>860</v>
       </c>
       <c r="O106" s="32" t="s">
-        <v>521</v>
+        <v>561</v>
       </c>
       <c r="P106" s="32" t="s">
-        <v>586</v>
+        <v>691</v>
       </c>
       <c r="Q106" s="32"/>
       <c r="R106" s="32" t="s">
-        <v>626</v>
+        <v>770</v>
       </c>
       <c r="S106" s="39"/>
       <c r="V106" s="15"/>
@@ -7979,45 +8986,45 @@
     <row r="108" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B108" s="25"/>
       <c r="D108" s="26" t="s">
-        <v>71</v>
+        <v>771</v>
       </c>
       <c r="E108" s="26" t="s">
-        <v>341</v>
+        <v>580</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>382</v>
+        <v>674</v>
       </c>
       <c r="G108" s="26"/>
       <c r="H108" s="26" t="s">
-        <v>381</v>
+        <v>670</v>
       </c>
       <c r="I108" s="26" t="s">
-        <v>429</v>
+        <v>773</v>
       </c>
       <c r="J108" s="26" t="s">
-        <v>470</v>
+        <v>861</v>
       </c>
       <c r="K108" s="26" t="s">
-        <v>471</v>
+        <v>863</v>
       </c>
       <c r="L108" s="26" t="s">
-        <v>472</v>
+        <v>865</v>
       </c>
       <c r="M108" s="26" t="s">
-        <v>473</v>
+        <v>867</v>
       </c>
       <c r="N108" s="26"/>
       <c r="O108" s="26" t="s">
-        <v>474</v>
+        <v>869</v>
       </c>
       <c r="P108" s="26" t="s">
-        <v>401</v>
+        <v>714</v>
       </c>
       <c r="Q108" s="26" t="s">
-        <v>475</v>
+        <v>871</v>
       </c>
       <c r="R108" s="26" t="s">
-        <v>476</v>
+        <v>873</v>
       </c>
       <c r="S108" s="27"/>
       <c r="V108" s="15"/>
@@ -8078,45 +9085,45 @@
     <row r="110" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B110" s="30"/>
       <c r="D110" s="32" t="s">
-        <v>627</v>
+        <v>772</v>
       </c>
       <c r="E110" s="32" t="s">
-        <v>531</v>
+        <v>581</v>
       </c>
       <c r="F110" s="32" t="s">
-        <v>578</v>
+        <v>675</v>
       </c>
       <c r="G110" s="32"/>
       <c r="H110" s="32" t="s">
-        <v>576</v>
+        <v>671</v>
       </c>
       <c r="I110" s="32" t="s">
-        <v>628</v>
+        <v>774</v>
       </c>
       <c r="J110" s="32" t="s">
-        <v>673</v>
+        <v>862</v>
       </c>
       <c r="K110" s="32" t="s">
-        <v>674</v>
+        <v>864</v>
       </c>
       <c r="L110" s="32" t="s">
-        <v>675</v>
+        <v>866</v>
       </c>
       <c r="M110" s="32" t="s">
-        <v>676</v>
+        <v>868</v>
       </c>
       <c r="N110" s="32"/>
       <c r="O110" s="32" t="s">
-        <v>677</v>
+        <v>870</v>
       </c>
       <c r="P110" s="32" t="s">
-        <v>598</v>
+        <v>715</v>
       </c>
       <c r="Q110" s="32" t="s">
-        <v>678</v>
+        <v>872</v>
       </c>
       <c r="R110" s="32" t="s">
-        <v>679</v>
+        <v>874</v>
       </c>
       <c r="S110" s="39"/>
       <c r="V110" s="15"/>
@@ -8145,35 +9152,35 @@
       <c r="B112" s="25"/>
       <c r="D112" s="26"/>
       <c r="E112" s="26" t="s">
-        <v>477</v>
+        <v>875</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>478</v>
+        <v>877</v>
       </c>
       <c r="G112" s="26" t="s">
-        <v>479</v>
+        <v>879</v>
       </c>
       <c r="H112" s="26" t="s">
-        <v>407</v>
+        <v>725</v>
       </c>
       <c r="I112" s="26"/>
       <c r="J112" s="26" t="s">
-        <v>60</v>
+        <v>584</v>
       </c>
       <c r="K112" s="26" t="s">
-        <v>480</v>
+        <v>881</v>
       </c>
       <c r="L112" s="26" t="s">
-        <v>481</v>
+        <v>883</v>
       </c>
       <c r="M112" s="26" t="s">
-        <v>481</v>
+        <v>883</v>
       </c>
       <c r="N112" s="26" t="s">
-        <v>440</v>
+        <v>799</v>
       </c>
       <c r="O112" s="26" t="s">
-        <v>354</v>
+        <v>613</v>
       </c>
       <c r="P112" s="26"/>
       <c r="Q112" s="26"/>
@@ -8226,7 +9233,7 @@
         <v>38</v>
       </c>
       <c r="Q113" s="51" t="s">
-        <v>729</v>
+        <v>520</v>
       </c>
       <c r="R113" s="51"/>
       <c r="S113" s="29"/>
@@ -8236,35 +9243,35 @@
       <c r="B114" s="30"/>
       <c r="D114" s="32"/>
       <c r="E114" s="32" t="s">
-        <v>680</v>
+        <v>876</v>
       </c>
       <c r="F114" s="32" t="s">
-        <v>681</v>
+        <v>878</v>
       </c>
       <c r="G114" s="32" t="s">
-        <v>682</v>
+        <v>880</v>
       </c>
       <c r="H114" s="32" t="s">
-        <v>604</v>
+        <v>726</v>
       </c>
       <c r="I114" s="32"/>
       <c r="J114" s="32" t="s">
-        <v>533</v>
+        <v>585</v>
       </c>
       <c r="K114" s="32" t="s">
-        <v>683</v>
+        <v>882</v>
       </c>
       <c r="L114" s="32" t="s">
-        <v>684</v>
+        <v>884</v>
       </c>
       <c r="M114" s="32" t="s">
-        <v>684</v>
+        <v>884</v>
       </c>
       <c r="N114" s="32" t="s">
-        <v>641</v>
+        <v>800</v>
       </c>
       <c r="O114" s="32" t="s">
-        <v>548</v>
+        <v>614</v>
       </c>
       <c r="P114" s="32"/>
       <c r="Q114" s="32"/>
@@ -8318,7 +9325,7 @@
         <v>29</v>
       </c>
       <c r="D117" s="51" t="s">
-        <v>729</v>
+        <v>520</v>
       </c>
       <c r="E117" s="51"/>
       <c r="F117" s="53"/>
@@ -8380,45 +9387,45 @@
     <row r="120" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B120" s="25"/>
       <c r="D120" s="26" t="s">
-        <v>482</v>
+        <v>885</v>
       </c>
       <c r="E120" s="26" t="s">
-        <v>358</v>
+        <v>621</v>
       </c>
       <c r="F120" s="26"/>
       <c r="G120" s="26" t="s">
-        <v>352</v>
+        <v>607</v>
       </c>
       <c r="H120" s="26" t="s">
-        <v>483</v>
+        <v>887</v>
       </c>
       <c r="I120" s="26" t="s">
-        <v>484</v>
+        <v>889</v>
       </c>
       <c r="J120" s="26" t="s">
-        <v>485</v>
+        <v>891</v>
       </c>
       <c r="K120" s="26" t="s">
-        <v>78</v>
+        <v>558</v>
       </c>
       <c r="L120" s="26" t="s">
-        <v>78</v>
+        <v>558</v>
       </c>
       <c r="M120" s="26" t="s">
-        <v>356</v>
+        <v>617</v>
       </c>
       <c r="N120" s="26" t="s">
-        <v>470</v>
+        <v>861</v>
       </c>
       <c r="O120" s="26"/>
       <c r="P120" s="26" t="s">
-        <v>460</v>
+        <v>839</v>
       </c>
       <c r="Q120" s="26" t="s">
-        <v>399</v>
+        <v>710</v>
       </c>
       <c r="R120" s="26" t="s">
-        <v>486</v>
+        <v>893</v>
       </c>
       <c r="S120" s="27"/>
       <c r="V120" s="15"/>
@@ -8479,45 +9486,45 @@
     <row r="122" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B122" s="30"/>
       <c r="D122" s="32" t="s">
-        <v>685</v>
+        <v>886</v>
       </c>
       <c r="E122" s="32" t="s">
-        <v>552</v>
+        <v>622</v>
       </c>
       <c r="F122" s="32"/>
       <c r="G122" s="32" t="s">
-        <v>545</v>
+        <v>608</v>
       </c>
       <c r="H122" s="32" t="s">
-        <v>686</v>
+        <v>888</v>
       </c>
       <c r="I122" s="32" t="s">
-        <v>687</v>
+        <v>890</v>
       </c>
       <c r="J122" s="32" t="s">
-        <v>688</v>
+        <v>892</v>
       </c>
       <c r="K122" s="32" t="s">
-        <v>520</v>
+        <v>559</v>
       </c>
       <c r="L122" s="32" t="s">
-        <v>520</v>
+        <v>559</v>
       </c>
       <c r="M122" s="32" t="s">
-        <v>550</v>
+        <v>618</v>
       </c>
       <c r="N122" s="32" t="s">
-        <v>673</v>
+        <v>862</v>
       </c>
       <c r="O122" s="32"/>
       <c r="P122" s="32" t="s">
-        <v>662</v>
+        <v>840</v>
       </c>
       <c r="Q122" s="32" t="s">
-        <v>596</v>
+        <v>711</v>
       </c>
       <c r="R122" s="32" t="s">
-        <v>689</v>
+        <v>894</v>
       </c>
       <c r="S122" s="39"/>
       <c r="V122" s="15"/>
@@ -8545,43 +9552,43 @@
     <row r="124" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B124" s="25"/>
       <c r="D124" s="26" t="s">
-        <v>440</v>
+        <v>799</v>
       </c>
       <c r="E124" s="26" t="s">
-        <v>356</v>
+        <v>617</v>
       </c>
       <c r="F124" s="26" t="s">
-        <v>67</v>
+        <v>895</v>
       </c>
       <c r="G124" s="26"/>
       <c r="H124" s="26" t="s">
-        <v>50</v>
+        <v>560</v>
       </c>
       <c r="I124" s="26" t="s">
-        <v>487</v>
+        <v>897</v>
       </c>
       <c r="J124" s="26"/>
       <c r="K124" s="26" t="s">
-        <v>405</v>
+        <v>721</v>
       </c>
       <c r="L124" s="26" t="s">
-        <v>354</v>
+        <v>613</v>
       </c>
       <c r="M124" s="26" t="s">
-        <v>397</v>
+        <v>706</v>
       </c>
       <c r="N124" s="26" t="s">
-        <v>480</v>
+        <v>881</v>
       </c>
       <c r="O124" s="26"/>
       <c r="P124" s="26" t="s">
-        <v>405</v>
+        <v>721</v>
       </c>
       <c r="Q124" s="26" t="s">
-        <v>354</v>
+        <v>613</v>
       </c>
       <c r="R124" s="26" t="s">
-        <v>488</v>
+        <v>899</v>
       </c>
       <c r="S124" s="27"/>
       <c r="V124" s="15"/>
@@ -8642,43 +9649,43 @@
     <row r="126" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B126" s="30"/>
       <c r="D126" s="32" t="s">
-        <v>641</v>
+        <v>800</v>
       </c>
       <c r="E126" s="32" t="s">
-        <v>550</v>
+        <v>618</v>
       </c>
       <c r="F126" s="32" t="s">
-        <v>690</v>
+        <v>896</v>
       </c>
       <c r="G126" s="32"/>
       <c r="H126" s="32" t="s">
-        <v>521</v>
+        <v>561</v>
       </c>
       <c r="I126" s="32" t="s">
-        <v>691</v>
+        <v>898</v>
       </c>
       <c r="J126" s="32"/>
       <c r="K126" s="32" t="s">
-        <v>602</v>
+        <v>722</v>
       </c>
       <c r="L126" s="32" t="s">
-        <v>548</v>
+        <v>614</v>
       </c>
       <c r="M126" s="32" t="s">
-        <v>594</v>
+        <v>707</v>
       </c>
       <c r="N126" s="32" t="s">
-        <v>683</v>
+        <v>882</v>
       </c>
       <c r="O126" s="32"/>
       <c r="P126" s="32" t="s">
-        <v>602</v>
+        <v>722</v>
       </c>
       <c r="Q126" s="32" t="s">
-        <v>548</v>
+        <v>614</v>
       </c>
       <c r="R126" s="32" t="s">
-        <v>692</v>
+        <v>900</v>
       </c>
       <c r="S126" s="39"/>
       <c r="V126" s="15"/>
@@ -8706,43 +9713,43 @@
     <row r="128" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B128" s="25"/>
       <c r="D128" s="26" t="s">
-        <v>61</v>
+        <v>797</v>
       </c>
       <c r="E128" s="26"/>
       <c r="F128" s="26" t="s">
-        <v>436</v>
+        <v>787</v>
       </c>
       <c r="G128" s="26" t="s">
-        <v>489</v>
+        <v>901</v>
       </c>
       <c r="H128" s="26" t="s">
-        <v>490</v>
+        <v>525</v>
       </c>
       <c r="I128" s="26" t="s">
-        <v>356</v>
+        <v>617</v>
       </c>
       <c r="J128" s="26" t="s">
-        <v>65</v>
+        <v>903</v>
       </c>
       <c r="K128" s="26"/>
       <c r="L128" s="26" t="s">
-        <v>381</v>
+        <v>670</v>
       </c>
       <c r="M128" s="26" t="s">
-        <v>434</v>
+        <v>783</v>
       </c>
       <c r="N128" s="26" t="s">
-        <v>60</v>
+        <v>584</v>
       </c>
       <c r="O128" s="26" t="s">
-        <v>70</v>
+        <v>905</v>
       </c>
       <c r="P128" s="26"/>
       <c r="Q128" s="26" t="s">
-        <v>380</v>
+        <v>668</v>
       </c>
       <c r="R128" s="26" t="s">
-        <v>369</v>
+        <v>646</v>
       </c>
       <c r="S128" s="27"/>
       <c r="V128" s="15"/>
@@ -8803,43 +9810,43 @@
     <row r="130" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B130" s="30"/>
       <c r="D130" s="32" t="s">
-        <v>640</v>
+        <v>798</v>
       </c>
       <c r="E130" s="32"/>
       <c r="F130" s="32" t="s">
-        <v>635</v>
+        <v>788</v>
       </c>
       <c r="G130" s="32" t="s">
-        <v>693</v>
+        <v>902</v>
       </c>
       <c r="H130" s="32" t="s">
-        <v>694</v>
+        <v>592</v>
       </c>
       <c r="I130" s="32" t="s">
-        <v>550</v>
+        <v>618</v>
       </c>
       <c r="J130" s="32" t="s">
-        <v>695</v>
+        <v>904</v>
       </c>
       <c r="K130" s="32"/>
       <c r="L130" s="32" t="s">
-        <v>576</v>
+        <v>671</v>
       </c>
       <c r="M130" s="32" t="s">
-        <v>633</v>
+        <v>784</v>
       </c>
       <c r="N130" s="32" t="s">
-        <v>533</v>
+        <v>585</v>
       </c>
       <c r="O130" s="32" t="s">
-        <v>696</v>
+        <v>906</v>
       </c>
       <c r="P130" s="32"/>
       <c r="Q130" s="32" t="s">
-        <v>575</v>
+        <v>669</v>
       </c>
       <c r="R130" s="32" t="s">
-        <v>564</v>
+        <v>647</v>
       </c>
       <c r="S130" s="39"/>
       <c r="V130" s="15"/>
@@ -8867,43 +9874,43 @@
     <row r="132" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B132" s="25"/>
       <c r="D132" s="26" t="s">
-        <v>364</v>
+        <v>635</v>
       </c>
       <c r="E132" s="26" t="s">
-        <v>356</v>
+        <v>617</v>
       </c>
       <c r="F132" s="26" t="s">
-        <v>365</v>
+        <v>638</v>
       </c>
       <c r="G132" s="26"/>
       <c r="H132" s="26" t="s">
-        <v>381</v>
+        <v>670</v>
       </c>
       <c r="I132" s="26" t="s">
-        <v>434</v>
+        <v>783</v>
       </c>
       <c r="J132" s="26" t="s">
-        <v>60</v>
+        <v>584</v>
       </c>
       <c r="K132" s="26" t="s">
-        <v>491</v>
+        <v>907</v>
       </c>
       <c r="L132" s="26"/>
       <c r="M132" s="26" t="s">
-        <v>68</v>
+        <v>909</v>
       </c>
       <c r="N132" s="26" t="s">
-        <v>492</v>
+        <v>911</v>
       </c>
       <c r="O132" s="26" t="s">
-        <v>493</v>
+        <v>913</v>
       </c>
       <c r="P132" s="26" t="s">
-        <v>434</v>
+        <v>783</v>
       </c>
       <c r="Q132" s="26"/>
       <c r="R132" s="26" t="s">
-        <v>494</v>
+        <v>915</v>
       </c>
       <c r="S132" s="27"/>
       <c r="V132" s="15"/>
@@ -8964,43 +9971,43 @@
     <row r="134" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B134" s="30"/>
       <c r="D134" s="32" t="s">
-        <v>559</v>
+        <v>636</v>
       </c>
       <c r="E134" s="32" t="s">
-        <v>550</v>
+        <v>618</v>
       </c>
       <c r="F134" s="32" t="s">
-        <v>560</v>
+        <v>639</v>
       </c>
       <c r="G134" s="32"/>
       <c r="H134" s="32" t="s">
-        <v>576</v>
+        <v>671</v>
       </c>
       <c r="I134" s="32" t="s">
-        <v>633</v>
+        <v>784</v>
       </c>
       <c r="J134" s="32" t="s">
-        <v>533</v>
+        <v>585</v>
       </c>
       <c r="K134" s="32" t="s">
-        <v>697</v>
+        <v>908</v>
       </c>
       <c r="L134" s="32"/>
       <c r="M134" s="32" t="s">
-        <v>698</v>
+        <v>910</v>
       </c>
       <c r="N134" s="32" t="s">
-        <v>699</v>
+        <v>912</v>
       </c>
       <c r="O134" s="32" t="s">
-        <v>700</v>
+        <v>914</v>
       </c>
       <c r="P134" s="32" t="s">
-        <v>633</v>
+        <v>784</v>
       </c>
       <c r="Q134" s="32"/>
       <c r="R134" s="32" t="s">
-        <v>701</v>
+        <v>916</v>
       </c>
       <c r="S134" s="39"/>
       <c r="V134" s="15"/>
@@ -9028,42 +10035,42 @@
     <row r="136" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B136" s="25"/>
       <c r="D136" s="26" t="s">
-        <v>493</v>
+        <v>913</v>
       </c>
       <c r="E136" s="26" t="s">
-        <v>434</v>
+        <v>783</v>
       </c>
       <c r="F136" s="26"/>
       <c r="G136" s="26" t="s">
-        <v>386</v>
+        <v>682</v>
       </c>
       <c r="H136" s="26" t="s">
-        <v>381</v>
+        <v>670</v>
       </c>
       <c r="I136" s="26" t="s">
-        <v>50</v>
+        <v>560</v>
       </c>
       <c r="J136" s="26" t="s">
-        <v>495</v>
+        <v>917</v>
       </c>
       <c r="K136" s="26" t="s">
-        <v>439</v>
+        <v>795</v>
       </c>
       <c r="L136" s="26" t="s">
-        <v>469</v>
+        <v>859</v>
       </c>
       <c r="M136" s="26" t="s">
-        <v>496</v>
+        <v>919</v>
       </c>
       <c r="N136" s="26"/>
       <c r="O136" s="26" t="s">
-        <v>60</v>
+        <v>584</v>
       </c>
       <c r="P136" s="26" t="s">
-        <v>497</v>
+        <v>921</v>
       </c>
       <c r="Q136" s="26" t="s">
-        <v>329</v>
+        <v>550</v>
       </c>
       <c r="R136" s="26"/>
       <c r="S136" s="27"/>
@@ -9125,42 +10132,42 @@
     <row r="138" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B138" s="30"/>
       <c r="D138" s="32" t="s">
-        <v>700</v>
+        <v>914</v>
       </c>
       <c r="E138" s="32" t="s">
-        <v>633</v>
+        <v>784</v>
       </c>
       <c r="F138" s="32"/>
       <c r="G138" s="32" t="s">
-        <v>582</v>
+        <v>683</v>
       </c>
       <c r="H138" s="32" t="s">
-        <v>576</v>
+        <v>671</v>
       </c>
       <c r="I138" s="32" t="s">
-        <v>521</v>
+        <v>561</v>
       </c>
       <c r="J138" s="32" t="s">
-        <v>702</v>
+        <v>918</v>
       </c>
       <c r="K138" s="32" t="s">
-        <v>639</v>
+        <v>796</v>
       </c>
       <c r="L138" s="32" t="s">
-        <v>672</v>
+        <v>860</v>
       </c>
       <c r="M138" s="32" t="s">
-        <v>703</v>
+        <v>920</v>
       </c>
       <c r="N138" s="32"/>
       <c r="O138" s="32" t="s">
-        <v>533</v>
+        <v>585</v>
       </c>
       <c r="P138" s="32" t="s">
-        <v>704</v>
+        <v>922</v>
       </c>
       <c r="Q138" s="32" t="s">
-        <v>516</v>
+        <v>551</v>
       </c>
       <c r="R138" s="32"/>
       <c r="S138" s="39"/>
@@ -9190,44 +10197,44 @@
       <c r="B140" s="25"/>
       <c r="D140" s="26"/>
       <c r="E140" s="26" t="s">
-        <v>498</v>
+        <v>923</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>446</v>
+        <v>811</v>
       </c>
       <c r="G140" s="26" t="s">
-        <v>445</v>
+        <v>809</v>
       </c>
       <c r="H140" s="26" t="s">
-        <v>356</v>
+        <v>617</v>
       </c>
       <c r="I140" s="26" t="s">
-        <v>434</v>
+        <v>783</v>
       </c>
       <c r="J140" s="26" t="s">
-        <v>439</v>
+        <v>795</v>
       </c>
       <c r="K140" s="26" t="s">
-        <v>434</v>
+        <v>783</v>
       </c>
       <c r="L140" s="26"/>
       <c r="M140" s="26" t="s">
-        <v>72</v>
+        <v>855</v>
       </c>
       <c r="N140" s="26" t="s">
-        <v>446</v>
+        <v>811</v>
       </c>
       <c r="O140" s="26" t="s">
-        <v>445</v>
+        <v>809</v>
       </c>
       <c r="P140" s="26" t="s">
-        <v>356</v>
+        <v>617</v>
       </c>
       <c r="Q140" s="26" t="s">
-        <v>469</v>
+        <v>859</v>
       </c>
       <c r="R140" s="26" t="s">
-        <v>439</v>
+        <v>795</v>
       </c>
       <c r="S140" s="27"/>
       <c r="V140" s="15"/>
@@ -9289,44 +10296,44 @@
       <c r="B142" s="30"/>
       <c r="D142" s="32"/>
       <c r="E142" s="32" t="s">
-        <v>705</v>
+        <v>924</v>
       </c>
       <c r="F142" s="32" t="s">
-        <v>648</v>
+        <v>812</v>
       </c>
       <c r="G142" s="32" t="s">
-        <v>647</v>
+        <v>810</v>
       </c>
       <c r="H142" s="32" t="s">
-        <v>550</v>
+        <v>618</v>
       </c>
       <c r="I142" s="32" t="s">
-        <v>633</v>
+        <v>784</v>
       </c>
       <c r="J142" s="32" t="s">
-        <v>639</v>
+        <v>796</v>
       </c>
       <c r="K142" s="32" t="s">
-        <v>633</v>
+        <v>784</v>
       </c>
       <c r="L142" s="32"/>
       <c r="M142" s="32" t="s">
-        <v>670</v>
+        <v>856</v>
       </c>
       <c r="N142" s="32" t="s">
-        <v>648</v>
+        <v>812</v>
       </c>
       <c r="O142" s="32" t="s">
-        <v>647</v>
+        <v>810</v>
       </c>
       <c r="P142" s="32" t="s">
-        <v>550</v>
+        <v>618</v>
       </c>
       <c r="Q142" s="32" t="s">
-        <v>672</v>
+        <v>860</v>
       </c>
       <c r="R142" s="32" t="s">
-        <v>639</v>
+        <v>796</v>
       </c>
       <c r="S142" s="39"/>
       <c r="V142" s="15"/>
@@ -9354,38 +10361,38 @@
     <row r="144" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B144" s="25"/>
       <c r="D144" s="26" t="s">
-        <v>469</v>
+        <v>859</v>
       </c>
       <c r="E144" s="26"/>
       <c r="F144" s="26" t="s">
-        <v>473</v>
+        <v>867</v>
       </c>
       <c r="G144" s="26"/>
       <c r="H144" s="26" t="s">
-        <v>722</v>
+        <v>513</v>
       </c>
       <c r="I144" s="26"/>
       <c r="J144" s="26" t="s">
-        <v>499</v>
+        <v>925</v>
       </c>
       <c r="K144" s="26" t="s">
-        <v>71</v>
+        <v>771</v>
       </c>
       <c r="L144" s="26" t="s">
-        <v>78</v>
+        <v>558</v>
       </c>
       <c r="M144" s="26"/>
       <c r="N144" s="26" t="s">
-        <v>500</v>
+        <v>927</v>
       </c>
       <c r="O144" s="26" t="s">
-        <v>452</v>
+        <v>823</v>
       </c>
       <c r="P144" s="26" t="s">
-        <v>352</v>
+        <v>607</v>
       </c>
       <c r="Q144" s="26" t="s">
-        <v>501</v>
+        <v>929</v>
       </c>
       <c r="R144" s="26"/>
       <c r="S144" s="27"/>
@@ -9447,38 +10454,38 @@
     <row r="146" spans="2:22" s="14" customFormat="1" ht="36" customHeight="1">
       <c r="B146" s="30"/>
       <c r="D146" s="32" t="s">
-        <v>672</v>
+        <v>860</v>
       </c>
       <c r="E146" s="32"/>
       <c r="F146" s="32" t="s">
-        <v>676</v>
+        <v>868</v>
       </c>
       <c r="G146" s="32"/>
       <c r="H146" s="32" t="s">
-        <v>730</v>
+        <v>521</v>
       </c>
       <c r="I146" s="32"/>
       <c r="J146" s="32" t="s">
-        <v>706</v>
+        <v>926</v>
       </c>
       <c r="K146" s="32" t="s">
-        <v>627</v>
+        <v>772</v>
       </c>
       <c r="L146" s="32" t="s">
-        <v>520</v>
+        <v>559</v>
       </c>
       <c r="M146" s="32"/>
       <c r="N146" s="32" t="s">
-        <v>707</v>
+        <v>928</v>
       </c>
       <c r="O146" s="32" t="s">
-        <v>654</v>
+        <v>824</v>
       </c>
       <c r="P146" s="32" t="s">
-        <v>545</v>
+        <v>608</v>
       </c>
       <c r="Q146" s="32" t="s">
-        <v>708</v>
+        <v>930</v>
       </c>
       <c r="R146" s="32"/>
       <c r="S146" s="39"/>
@@ -11605,7 +12612,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE1D3C5A-9A9F-4993-BA48-0CEBF522BB86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6ED3FE0-A7F7-4354-951F-22F08195F85D}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
@@ -11628,10 +12635,10 @@
         <v>135</v>
       </c>
       <c r="B2" t="s">
-        <v>716</v>
+        <v>637</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -11639,10 +12646,10 @@
         <v>147</v>
       </c>
       <c r="B3" t="s">
-        <v>402</v>
+        <v>637</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -11650,10 +12657,10 @@
         <v>181</v>
       </c>
       <c r="B4" t="s">
-        <v>717</v>
+        <v>637</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -11661,10 +12668,10 @@
         <v>204</v>
       </c>
       <c r="B5" t="s">
-        <v>718</v>
+        <v>637</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -11672,10 +12679,10 @@
         <v>222</v>
       </c>
       <c r="B6" t="s">
-        <v>719</v>
+        <v>637</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -11683,10 +12690,10 @@
         <v>250</v>
       </c>
       <c r="B7" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -11694,10 +12701,10 @@
         <v>252</v>
       </c>
       <c r="B8" t="s">
-        <v>721</v>
+        <v>637</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -11705,10 +12712,10 @@
         <v>313</v>
       </c>
       <c r="B9" t="s">
-        <v>722</v>
+        <v>637</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -11718,8 +12725,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5171F7A5-3314-4C75-98D8-09CB1FA58B28}">
-  <dimension ref="A1:D1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F47B1E8-E17B-4F0F-8F53-55CEF3A5416C}">
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -11734,6 +12741,50 @@
       </c>
       <c r="D1" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" t="s">
+        <v>586</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -11743,7 +12794,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49355E6-4F77-4AF5-A5C6-2B188104B7C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB90EF23-7AF1-4F22-986E-727539437AA1}">
   <dimension ref="A1:D238"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
@@ -11777,7 +12828,7 @@
         <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>319</v>
+        <v>528</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -11799,7 +12850,7 @@
         <v>88</v>
       </c>
       <c r="B5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -11810,7 +12861,7 @@
         <v>89</v>
       </c>
       <c r="B6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -11821,7 +12872,7 @@
         <v>90</v>
       </c>
       <c r="B7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -11832,7 +12883,7 @@
         <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -11843,7 +12894,7 @@
         <v>91</v>
       </c>
       <c r="B9" t="s">
-        <v>324</v>
+        <v>440</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -11854,7 +12905,7 @@
         <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -11865,7 +12916,7 @@
         <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -11876,7 +12927,7 @@
         <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -11898,7 +12949,7 @@
         <v>96</v>
       </c>
       <c r="B14" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -11909,7 +12960,7 @@
         <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -11920,7 +12971,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -11931,7 +12982,7 @@
         <v>98</v>
       </c>
       <c r="B17" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -11942,7 +12993,7 @@
         <v>99</v>
       </c>
       <c r="B18" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -11975,7 +13026,7 @@
         <v>100</v>
       </c>
       <c r="B21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -11997,7 +13048,7 @@
         <v>102</v>
       </c>
       <c r="B23" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -12008,7 +13059,7 @@
         <v>103</v>
       </c>
       <c r="B24" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -12019,7 +13070,7 @@
         <v>104</v>
       </c>
       <c r="B25" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -12030,7 +13081,7 @@
         <v>105</v>
       </c>
       <c r="B26" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -12041,7 +13092,7 @@
         <v>106</v>
       </c>
       <c r="B27" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -12052,7 +13103,7 @@
         <v>107</v>
       </c>
       <c r="B28" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -12063,7 +13114,7 @@
         <v>108</v>
       </c>
       <c r="B29" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -12074,7 +13125,7 @@
         <v>109</v>
       </c>
       <c r="B30" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C30">
         <v>4</v>
@@ -12085,7 +13136,7 @@
         <v>110</v>
       </c>
       <c r="B31" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -12107,7 +13158,7 @@
         <v>112</v>
       </c>
       <c r="B33" t="s">
-        <v>343</v>
+        <v>586</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -12118,7 +13169,7 @@
         <v>113</v>
       </c>
       <c r="B34" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -12129,7 +13180,7 @@
         <v>114</v>
       </c>
       <c r="B35" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -12140,7 +13191,7 @@
         <v>115</v>
       </c>
       <c r="B36" t="s">
-        <v>346</v>
+        <v>486</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -12151,7 +13202,7 @@
         <v>116</v>
       </c>
       <c r="B37" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -12162,7 +13213,7 @@
         <v>117</v>
       </c>
       <c r="B38" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -12173,7 +13224,7 @@
         <v>118</v>
       </c>
       <c r="B39" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -12184,7 +13235,7 @@
         <v>119</v>
       </c>
       <c r="B40" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -12195,7 +13246,7 @@
         <v>120</v>
       </c>
       <c r="B41" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -12228,7 +13279,7 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C44">
         <v>3</v>
@@ -12239,7 +13290,7 @@
         <v>123</v>
       </c>
       <c r="B45" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -12261,7 +13312,7 @@
         <v>124</v>
       </c>
       <c r="B47" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C47">
         <v>3</v>
@@ -12272,7 +13323,7 @@
         <v>125</v>
       </c>
       <c r="B48" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -12283,7 +13334,7 @@
         <v>126</v>
       </c>
       <c r="B49" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C49">
         <v>10</v>
@@ -12294,7 +13345,7 @@
         <v>127</v>
       </c>
       <c r="B50" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -12305,7 +13356,7 @@
         <v>128</v>
       </c>
       <c r="B51" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -12327,7 +13378,7 @@
         <v>130</v>
       </c>
       <c r="B53" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -12338,7 +13389,7 @@
         <v>131</v>
       </c>
       <c r="B54" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -12349,7 +13400,7 @@
         <v>132</v>
       </c>
       <c r="B55" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -12360,7 +13411,7 @@
         <v>133</v>
       </c>
       <c r="B56" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -12371,7 +13422,7 @@
         <v>39</v>
       </c>
       <c r="B57" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C57">
         <v>3</v>
@@ -12382,7 +13433,7 @@
         <v>134</v>
       </c>
       <c r="B58" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -12393,7 +13444,7 @@
         <v>136</v>
       </c>
       <c r="B59" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -12404,7 +13455,7 @@
         <v>137</v>
       </c>
       <c r="B60" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -12415,7 +13466,7 @@
         <v>138</v>
       </c>
       <c r="B61" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -12426,7 +13477,7 @@
         <v>139</v>
       </c>
       <c r="B62" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -12437,7 +13488,7 @@
         <v>140</v>
       </c>
       <c r="B63" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -12448,7 +13499,7 @@
         <v>141</v>
       </c>
       <c r="B64" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -12459,7 +13510,7 @@
         <v>142</v>
       </c>
       <c r="B65" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C65">
         <v>2</v>
@@ -12470,7 +13521,7 @@
         <v>143</v>
       </c>
       <c r="B66" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -12481,7 +13532,7 @@
         <v>34</v>
       </c>
       <c r="B67" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -12492,7 +13543,7 @@
         <v>144</v>
       </c>
       <c r="B68" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -12503,7 +13554,7 @@
         <v>145</v>
       </c>
       <c r="B69" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -12514,7 +13565,7 @@
         <v>146</v>
       </c>
       <c r="B70" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -12525,7 +13576,7 @@
         <v>148</v>
       </c>
       <c r="B71" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -12536,7 +13587,7 @@
         <v>149</v>
       </c>
       <c r="B72" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -12547,7 +13598,7 @@
         <v>150</v>
       </c>
       <c r="B73" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -12569,7 +13620,7 @@
         <v>152</v>
       </c>
       <c r="B75" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -12580,7 +13631,7 @@
         <v>153</v>
       </c>
       <c r="B76" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C76">
         <v>2</v>
@@ -12591,7 +13642,7 @@
         <v>154</v>
       </c>
       <c r="B77" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C77">
         <v>3</v>
@@ -12602,7 +13653,7 @@
         <v>155</v>
       </c>
       <c r="B78" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C78">
         <v>7</v>
@@ -12624,7 +13675,7 @@
         <v>156</v>
       </c>
       <c r="B80" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C80">
         <v>3</v>
@@ -12635,7 +13686,7 @@
         <v>157</v>
       </c>
       <c r="B81" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -12646,7 +13697,7 @@
         <v>158</v>
       </c>
       <c r="B82" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -12657,7 +13708,7 @@
         <v>159</v>
       </c>
       <c r="B83" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -12668,7 +13719,7 @@
         <v>160</v>
       </c>
       <c r="B84" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C84">
         <v>3</v>
@@ -12679,7 +13730,7 @@
         <v>161</v>
       </c>
       <c r="B85" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C85">
         <v>3</v>
@@ -12690,7 +13741,7 @@
         <v>162</v>
       </c>
       <c r="B86" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -12701,7 +13752,7 @@
         <v>163</v>
       </c>
       <c r="B87" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -12712,7 +13763,7 @@
         <v>164</v>
       </c>
       <c r="B88" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -12723,7 +13774,7 @@
         <v>165</v>
       </c>
       <c r="B89" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -12745,7 +13796,7 @@
         <v>166</v>
       </c>
       <c r="B91" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -12756,7 +13807,7 @@
         <v>167</v>
       </c>
       <c r="B92" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -12767,7 +13818,7 @@
         <v>168</v>
       </c>
       <c r="B93" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -12778,7 +13829,7 @@
         <v>169</v>
       </c>
       <c r="B94" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -12789,7 +13840,7 @@
         <v>170</v>
       </c>
       <c r="B95" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -12800,7 +13851,7 @@
         <v>171</v>
       </c>
       <c r="B96" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -12811,7 +13862,7 @@
         <v>172</v>
       </c>
       <c r="B97" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -12822,7 +13873,7 @@
         <v>173</v>
       </c>
       <c r="B98" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -12833,7 +13884,7 @@
         <v>174</v>
       </c>
       <c r="B99" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -12844,7 +13895,7 @@
         <v>175</v>
       </c>
       <c r="B100" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -12855,7 +13906,7 @@
         <v>176</v>
       </c>
       <c r="B101" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -12866,7 +13917,7 @@
         <v>177</v>
       </c>
       <c r="B102" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C102">
         <v>2</v>
@@ -12877,7 +13928,7 @@
         <v>178</v>
       </c>
       <c r="B103" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -12888,7 +13939,7 @@
         <v>180</v>
       </c>
       <c r="B104" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C104">
         <v>2</v>
@@ -12899,7 +13950,7 @@
         <v>182</v>
       </c>
       <c r="B105" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -12910,7 +13961,7 @@
         <v>183</v>
       </c>
       <c r="B106" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C106">
         <v>2</v>
@@ -12921,7 +13972,7 @@
         <v>184</v>
       </c>
       <c r="B107" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -12932,7 +13983,7 @@
         <v>185</v>
       </c>
       <c r="B108" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C108">
         <v>2</v>
@@ -12943,7 +13994,7 @@
         <v>186</v>
       </c>
       <c r="B109" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C109">
         <v>5</v>
@@ -12954,7 +14005,7 @@
         <v>187</v>
       </c>
       <c r="B110" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C110">
         <v>1</v>
@@ -12965,7 +14016,7 @@
         <v>188</v>
       </c>
       <c r="B111" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C111">
         <v>2</v>
@@ -12976,7 +14027,7 @@
         <v>189</v>
       </c>
       <c r="B112" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C112">
         <v>1</v>
@@ -12987,7 +14038,7 @@
         <v>190</v>
       </c>
       <c r="B113" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C113">
         <v>1</v>
@@ -12998,7 +14049,7 @@
         <v>191</v>
       </c>
       <c r="B114" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C114">
         <v>1</v>
@@ -13009,7 +14060,7 @@
         <v>192</v>
       </c>
       <c r="B115" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C115">
         <v>1</v>
@@ -13020,7 +14071,7 @@
         <v>193</v>
       </c>
       <c r="B116" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C116">
         <v>1</v>
@@ -13031,7 +14082,7 @@
         <v>194</v>
       </c>
       <c r="B117" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C117">
         <v>2</v>
@@ -13042,7 +14093,7 @@
         <v>28</v>
       </c>
       <c r="B118" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C118">
         <v>1</v>
@@ -13064,7 +14115,7 @@
         <v>196</v>
       </c>
       <c r="B120" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -13075,7 +14126,7 @@
         <v>197</v>
       </c>
       <c r="B121" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C121">
         <v>1</v>
@@ -13086,7 +14137,7 @@
         <v>198</v>
       </c>
       <c r="B122" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C122">
         <v>1</v>
@@ -13097,7 +14148,7 @@
         <v>199</v>
       </c>
       <c r="B123" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C123">
         <v>1</v>
@@ -13108,7 +14159,7 @@
         <v>200</v>
       </c>
       <c r="B124" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C124">
         <v>1</v>
@@ -13119,7 +14170,7 @@
         <v>201</v>
       </c>
       <c r="B125" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C125">
         <v>1</v>
@@ -13130,7 +14181,7 @@
         <v>202</v>
       </c>
       <c r="B126" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C126">
         <v>1</v>
@@ -13141,7 +14192,7 @@
         <v>203</v>
       </c>
       <c r="B127" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C127">
         <v>1</v>
@@ -13152,7 +14203,7 @@
         <v>205</v>
       </c>
       <c r="B128" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C128">
         <v>1</v>
@@ -13163,7 +14214,7 @@
         <v>206</v>
       </c>
       <c r="B129" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -13174,7 +14225,7 @@
         <v>207</v>
       </c>
       <c r="B130" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -13185,7 +14236,7 @@
         <v>208</v>
       </c>
       <c r="B131" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -13196,7 +14247,7 @@
         <v>209</v>
       </c>
       <c r="B132" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -13207,7 +14258,7 @@
         <v>210</v>
       </c>
       <c r="B133" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C133">
         <v>2</v>
@@ -13218,7 +14269,7 @@
         <v>211</v>
       </c>
       <c r="B134" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -13229,7 +14280,7 @@
         <v>212</v>
       </c>
       <c r="B135" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -13240,7 +14291,7 @@
         <v>213</v>
       </c>
       <c r="B136" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -13251,7 +14302,7 @@
         <v>214</v>
       </c>
       <c r="B137" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -13262,7 +14313,7 @@
         <v>215</v>
       </c>
       <c r="B138" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C138">
         <v>2</v>
@@ -13284,7 +14335,7 @@
         <v>27</v>
       </c>
       <c r="B140" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C140">
         <v>2</v>
@@ -13295,7 +14346,7 @@
         <v>217</v>
       </c>
       <c r="B141" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -13306,7 +14357,7 @@
         <v>218</v>
       </c>
       <c r="B142" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -13317,7 +14368,7 @@
         <v>219</v>
       </c>
       <c r="B143" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -13328,7 +14379,7 @@
         <v>220</v>
       </c>
       <c r="B144" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -13339,7 +14390,7 @@
         <v>221</v>
       </c>
       <c r="B145" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C145">
         <v>7</v>
@@ -13350,7 +14401,7 @@
         <v>223</v>
       </c>
       <c r="B146" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -13361,7 +14412,7 @@
         <v>224</v>
       </c>
       <c r="B147" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -13372,7 +14423,7 @@
         <v>225</v>
       </c>
       <c r="B148" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -13383,7 +14434,7 @@
         <v>226</v>
       </c>
       <c r="B149" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -13394,7 +14445,7 @@
         <v>227</v>
       </c>
       <c r="B150" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -13416,7 +14467,7 @@
         <v>228</v>
       </c>
       <c r="B152" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C152">
         <v>5</v>
@@ -13438,7 +14489,7 @@
         <v>230</v>
       </c>
       <c r="B154" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C154">
         <v>3</v>
@@ -13460,7 +14511,7 @@
         <v>231</v>
       </c>
       <c r="B156" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -13471,7 +14522,7 @@
         <v>232</v>
       </c>
       <c r="B157" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -13482,7 +14533,7 @@
         <v>233</v>
       </c>
       <c r="B158" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -13493,7 +14544,7 @@
         <v>234</v>
       </c>
       <c r="B159" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -13504,7 +14555,7 @@
         <v>235</v>
       </c>
       <c r="B160" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C160">
         <v>3</v>
@@ -13515,7 +14566,7 @@
         <v>236</v>
       </c>
       <c r="B161" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C161">
         <v>3</v>
@@ -13526,7 +14577,7 @@
         <v>237</v>
       </c>
       <c r="B162" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C162">
         <v>2</v>
@@ -13537,7 +14588,7 @@
         <v>238</v>
       </c>
       <c r="B163" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -13548,7 +14599,7 @@
         <v>239</v>
       </c>
       <c r="B164" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -13559,7 +14610,7 @@
         <v>240</v>
       </c>
       <c r="B165" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -13570,7 +14621,7 @@
         <v>241</v>
       </c>
       <c r="B166" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -13581,7 +14632,7 @@
         <v>242</v>
       </c>
       <c r="B167" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -13592,7 +14643,7 @@
         <v>243</v>
       </c>
       <c r="B168" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -13603,7 +14654,7 @@
         <v>244</v>
       </c>
       <c r="B169" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -13614,7 +14665,7 @@
         <v>245</v>
       </c>
       <c r="B170" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -13625,7 +14676,7 @@
         <v>246</v>
       </c>
       <c r="B171" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -13636,7 +14687,7 @@
         <v>247</v>
       </c>
       <c r="B172" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -13647,7 +14698,7 @@
         <v>248</v>
       </c>
       <c r="B173" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -13658,7 +14709,7 @@
         <v>249</v>
       </c>
       <c r="B174" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -13669,7 +14720,7 @@
         <v>251</v>
       </c>
       <c r="B175" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -13680,7 +14731,7 @@
         <v>253</v>
       </c>
       <c r="B176" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C176">
         <v>2</v>
@@ -13691,7 +14742,7 @@
         <v>254</v>
       </c>
       <c r="B177" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C177">
         <v>2</v>
@@ -13702,7 +14753,7 @@
         <v>255</v>
       </c>
       <c r="B178" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -13713,7 +14764,7 @@
         <v>256</v>
       </c>
       <c r="B179" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -13724,7 +14775,7 @@
         <v>257</v>
       </c>
       <c r="B180" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -13735,7 +14786,7 @@
         <v>258</v>
       </c>
       <c r="B181" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -13746,7 +14797,7 @@
         <v>259</v>
       </c>
       <c r="B182" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -13757,7 +14808,7 @@
         <v>260</v>
       </c>
       <c r="B183" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -13768,7 +14819,7 @@
         <v>261</v>
       </c>
       <c r="B184" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -13779,7 +14830,7 @@
         <v>262</v>
       </c>
       <c r="B185" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -13790,7 +14841,7 @@
         <v>263</v>
       </c>
       <c r="B186" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -13801,7 +14852,7 @@
         <v>264</v>
       </c>
       <c r="B187" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C187">
         <v>1</v>
@@ -13812,7 +14863,7 @@
         <v>265</v>
       </c>
       <c r="B188" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -13823,7 +14874,7 @@
         <v>266</v>
       </c>
       <c r="B189" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -13845,7 +14896,7 @@
         <v>268</v>
       </c>
       <c r="B191" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C191">
         <v>1</v>
@@ -13856,7 +14907,7 @@
         <v>269</v>
       </c>
       <c r="B192" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C192">
         <v>4</v>
@@ -13878,7 +14929,7 @@
         <v>271</v>
       </c>
       <c r="B194" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C194">
         <v>2</v>
@@ -13889,7 +14940,7 @@
         <v>272</v>
       </c>
       <c r="B195" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -13900,7 +14951,7 @@
         <v>273</v>
       </c>
       <c r="B196" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -13911,7 +14962,7 @@
         <v>274</v>
       </c>
       <c r="B197" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C197">
         <v>1</v>
@@ -13922,7 +14973,7 @@
         <v>275</v>
       </c>
       <c r="B198" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C198">
         <v>1</v>
@@ -13933,7 +14984,7 @@
         <v>276</v>
       </c>
       <c r="B199" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C199">
         <v>1</v>
@@ -13944,7 +14995,7 @@
         <v>277</v>
       </c>
       <c r="B200" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -13955,7 +15006,7 @@
         <v>278</v>
       </c>
       <c r="B201" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -13966,7 +15017,7 @@
         <v>279</v>
       </c>
       <c r="B202" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -13977,7 +15028,7 @@
         <v>280</v>
       </c>
       <c r="B203" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -13988,7 +15039,7 @@
         <v>281</v>
       </c>
       <c r="B204" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -13999,7 +15050,7 @@
         <v>282</v>
       </c>
       <c r="B205" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C205">
         <v>2</v>
@@ -14010,7 +15061,7 @@
         <v>283</v>
       </c>
       <c r="B206" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C206">
         <v>2</v>
@@ -14021,7 +15072,7 @@
         <v>284</v>
       </c>
       <c r="B207" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C207">
         <v>1</v>
@@ -14032,7 +15083,7 @@
         <v>286</v>
       </c>
       <c r="B208" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C208">
         <v>1</v>
@@ -14043,7 +15094,7 @@
         <v>287</v>
       </c>
       <c r="B209" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -14054,7 +15105,7 @@
         <v>288</v>
       </c>
       <c r="B210" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C210">
         <v>1</v>
@@ -14076,7 +15127,7 @@
         <v>290</v>
       </c>
       <c r="B212" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -14098,7 +15149,7 @@
         <v>292</v>
       </c>
       <c r="B214" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -14109,7 +15160,7 @@
         <v>293</v>
       </c>
       <c r="B215" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -14120,7 +15171,7 @@
         <v>294</v>
       </c>
       <c r="B216" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -14131,7 +15182,7 @@
         <v>295</v>
       </c>
       <c r="B217" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -14142,7 +15193,7 @@
         <v>296</v>
       </c>
       <c r="B218" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -14175,7 +15226,7 @@
         <v>298</v>
       </c>
       <c r="B221" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -14186,7 +15237,7 @@
         <v>299</v>
       </c>
       <c r="B222" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -14208,7 +15259,7 @@
         <v>300</v>
       </c>
       <c r="B224" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -14219,7 +15270,7 @@
         <v>301</v>
       </c>
       <c r="B225" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C225">
         <v>2</v>
@@ -14230,7 +15281,7 @@
         <v>302</v>
       </c>
       <c r="B226" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -14241,7 +15292,7 @@
         <v>303</v>
       </c>
       <c r="B227" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -14252,7 +15303,7 @@
         <v>304</v>
       </c>
       <c r="B228" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -14263,7 +15314,7 @@
         <v>305</v>
       </c>
       <c r="B229" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -14274,7 +15325,7 @@
         <v>306</v>
       </c>
       <c r="B230" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -14285,7 +15336,7 @@
         <v>309</v>
       </c>
       <c r="B231" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -14307,7 +15358,7 @@
         <v>312</v>
       </c>
       <c r="B233" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -14318,7 +15369,7 @@
         <v>314</v>
       </c>
       <c r="B234" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -14329,7 +15380,7 @@
         <v>315</v>
       </c>
       <c r="B235" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -14340,7 +15391,7 @@
         <v>316</v>
       </c>
       <c r="B236" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -14351,7 +15402,7 @@
         <v>36</v>
       </c>
       <c r="B237" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -14362,7 +15413,7 @@
         <v>317</v>
       </c>
       <c r="B238" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -14398,7 +15449,7 @@
         <v>135</v>
       </c>
       <c r="B2" t="s">
-        <v>709</v>
+        <v>500</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -14409,7 +15460,7 @@
         <v>147</v>
       </c>
       <c r="B3" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -14420,7 +15471,7 @@
         <v>181</v>
       </c>
       <c r="B4" t="s">
-        <v>710</v>
+        <v>501</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -14431,7 +15482,7 @@
         <v>204</v>
       </c>
       <c r="B5" t="s">
-        <v>711</v>
+        <v>502</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -14442,7 +15493,7 @@
         <v>222</v>
       </c>
       <c r="B6" t="s">
-        <v>712</v>
+        <v>503</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -14453,7 +15504,7 @@
         <v>250</v>
       </c>
       <c r="B7" t="s">
-        <v>713</v>
+        <v>504</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -14464,7 +15515,7 @@
         <v>252</v>
       </c>
       <c r="B8" t="s">
-        <v>714</v>
+        <v>505</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -14475,7 +15526,7 @@
         <v>313</v>
       </c>
       <c r="B9" t="s">
-        <v>715</v>
+        <v>506</v>
       </c>
       <c r="C9">
         <v>1</v>
